--- a/relevance_check.xlsx
+++ b/relevance_check.xlsx
@@ -6494,7 +6494,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -6534,102 +6534,118 @@
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <f aca="false">COUNTIFS(Ground!$C:$C,"core",Ground!$N:$N,"Include")</f>
-        <v>0</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <f aca="false">COUNTIFS(Ground!$C:$C,"recent",Ground!$N:$N,"Include")</f>
-        <v>0</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <f aca="false">COUNTIF(Ground!$N:$N,"Exclude")</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <f aca="false">COUNTIF(Ground!$N:$N,"Unsure")</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="str">
-        <f aca="false">IF(AND(B2&gt;=C2,D2&gt;=E2),"Done","In progress")</f>
-        <v>In progress</v>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <f aca="false">COUNTIFS(Air!$C:$C,"core",Air!$N:$N,"Include")</f>
-        <v>0</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <f aca="false">COUNTIFS(Air!$C:$C,"recent",Air!$N:$N,"Include")</f>
-        <v>0</v>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="n">
-        <f aca="false">COUNTIF(Air!$N:$N,"Exclude")</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <f aca="false">COUNTIF(Air!$N:$N,"Unsure")</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="str">
-        <f aca="false">IF(AND(B3&gt;=C3,D3&gt;=E3),"Done","In progress")</f>
-        <v>In progress</v>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <f aca="false">COUNTIFS(Maritime!$C:$C,"core",Maritime!$N:$N,"Include")</f>
-        <v>0</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <f aca="false">COUNTIFS(Maritime!$C:$C,"recent",Maritime!$N:$N,"Include")</f>
-        <v>0</v>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <f aca="false">COUNTIF(Maritime!$N:$N,"Exclude")</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <f aca="false">COUNTIF(Maritime!$N:$N,"Unsure")</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="str">
-        <f aca="false">IF(AND(B4&gt;=C4,D4&gt;=E4),"Done","In progress")</f>
-        <v>In progress</v>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <f aca="false">COUNTIF(Surveys!$N:$N,"Include")</f>
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>6</v>
@@ -6638,7 +6654,11 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
@@ -6657,7 +6677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -6766,9 +6786,21 @@
       <c r="M2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
@@ -6808,9 +6840,21 @@
       <c r="M3" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone RGB-IR vehicle detection + dataset</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -6850,9 +6894,21 @@
       <c r="M4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6G V2X survey; UAVs only in passing (E2)</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
@@ -6892,9 +6948,21 @@
       <c r="M5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV-ITS applications overview</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
@@ -6936,9 +7004,21 @@
       <c r="M6" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edge-intelligence ITS survey; UAV one scenario</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
@@ -6978,9 +7058,21 @@
       <c r="M7" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV road-safety/traffic review</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
@@ -7018,9 +7110,21 @@
       <c r="M8" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inD drone trajectory dataset</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -7060,9 +7164,21 @@
       <c r="M9" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VANET routing, not traffic sensing</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
@@ -7102,9 +7218,21 @@
       <c r="M10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pNEUMA</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
@@ -7144,9 +7272,21 @@
       <c r="M11" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small-object vehicle detection, UAV traffic</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
@@ -7188,9 +7328,21 @@
       <c r="M12" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vehicle-detection-from-UAV review</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
@@ -7230,9 +7382,21 @@
       <c r="M13" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VANET data-routing scheme</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
@@ -7274,9 +7438,21 @@
       <c r="M14" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Systematic review of surveillance drones</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
@@ -7316,9 +7492,21 @@
       <c r="M15" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vehicle trajectory extraction + tracking</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
@@ -7358,9 +7546,21 @@
       <c r="M16" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Car detection Faster R-CNN/YOLOv3</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
@@ -7400,9 +7600,21 @@
       <c r="M17" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV traffic surveillance system</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
@@ -7442,9 +7654,21 @@
       <c r="M18" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Authentication protocol (IoD)</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
@@ -7484,9 +7708,21 @@
       <c r="M19" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traffic flow parameter estimation + dataset</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
@@ -7524,9 +7760,21 @@
       <c r="M20" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exiD drone trajectory dataset</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
@@ -7566,9 +7814,21 @@
       <c r="M21" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blockchain energy trading</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
@@ -7606,9 +7866,21 @@
       <c r="M22" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rounD drone trajectory dataset</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
@@ -7648,9 +7920,21 @@
       <c r="M23" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV regulation policy review</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
@@ -7692,9 +7976,21 @@
       <c r="M24" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV-RIS wireless survey</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
@@ -7734,9 +8030,21 @@
       <c r="M25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6G task offloading / edge comms</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
@@ -7776,9 +8084,21 @@
       <c r="M26" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generic UAV data-collection scheme</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
@@ -7818,9 +8138,21 @@
       <c r="M27" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
+      <c r="N27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YOLOv5 real-time vehicle detection</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
@@ -7858,9 +8190,21 @@
       <c r="M28" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AU-AIR traffic surveillance dataset</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
@@ -7900,9 +8244,21 @@
       <c r="M29" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
+      <c r="N29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AoI/vehicular networking trajectory</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
@@ -7942,9 +8298,21 @@
       <c r="M30" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lane-change behaviour (flow analysis, highD)</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
@@ -7982,9 +8350,21 @@
       <c r="M31" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cellular-UAV wireless connectivity/security</t>
+        </is>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
@@ -8024,9 +8404,21 @@
       <c r="M32" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone-truck delivery routing</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
@@ -8066,9 +8458,21 @@
       <c r="M33" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Privacy-preserving authentication</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
@@ -8108,9 +8512,21 @@
       <c r="M34" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV content delivery/caching comms</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
@@ -8150,9 +8566,21 @@
       <c r="M35" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
+      <c r="N35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key management (authentication) IoV</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
@@ -8192,9 +8620,21 @@
       <c r="M36" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crash/incident prediction from UAV video</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
@@ -8234,9 +8674,21 @@
       <c r="M37" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone delivery scheduling</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
@@ -8274,9 +8726,21 @@
       <c r="M38" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
+      <c r="N38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIND signalized-intersection dataset</t>
+        </is>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
@@ -8316,9 +8780,21 @@
       <c r="M39" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
+      <c r="N39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logistics UAV delivery path planning</t>
+        </is>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
@@ -8358,9 +8834,21 @@
       <c r="M40" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YOLO-ViT IR vehicle detection</t>
+        </is>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
@@ -8400,9 +8888,21 @@
       <c r="M41" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
+      <c r="N41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV-MEC security offloading (PLS)</t>
+        </is>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
@@ -8442,9 +8942,21 @@
       <c r="M42" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
+      <c r="N42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road crack / pavement inspection</t>
+        </is>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
@@ -8484,9 +8996,21 @@
       <c r="M43" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="N43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Road-traffic multi-element detection</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
@@ -8526,9 +9050,21 @@
       <c r="M44" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
+      <c r="N44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traffic monitoring/surveillance DL (AU-AIR)</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
@@ -8568,9 +9104,21 @@
       <c r="M45" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
+      <c r="N45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-UAV road traffic monitoring + events (20th include; stop)</t>
+        </is>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
@@ -9706,9 +10254,21 @@
       <c r="M72" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="N72" s="9"/>
-      <c r="O72" s="9"/>
-      <c r="P72" s="9"/>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML-aided UAV ops survey</t>
+        </is>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
@@ -9748,9 +10308,21 @@
       <c r="M73" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="N73" s="9"/>
-      <c r="O73" s="9"/>
-      <c r="P73" s="9"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CitySim drone trajectory dataset</t>
+        </is>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
@@ -9790,9 +10362,21 @@
       <c r="M74" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="N74" s="9"/>
-      <c r="O74" s="9"/>
-      <c r="P74" s="9"/>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vehicle detection YOLOv8</t>
+        </is>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
@@ -9832,9 +10416,21 @@
       <c r="M75" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="N75" s="9"/>
-      <c r="O75" s="9"/>
-      <c r="P75" s="9"/>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aerial P2P / VANET data sharing</t>
+        </is>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
@@ -9874,9 +10470,21 @@
       <c r="M76" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="N76" s="9"/>
-      <c r="O76" s="9"/>
-      <c r="P76" s="9"/>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PVswin-YOLOv8s pedestrian/vehicle detection</t>
+        </is>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
@@ -9918,9 +10526,21 @@
       <c r="M77" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="N77" s="9"/>
-      <c r="O77" s="9"/>
-      <c r="P77" s="9"/>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crowdsensing smart-city survey</t>
+        </is>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
@@ -9960,9 +10580,21 @@
       <c r="M78" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="N78" s="9"/>
-      <c r="O78" s="9"/>
-      <c r="P78" s="9"/>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YOLOv8 traffic monitoring</t>
+        </is>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
@@ -10002,9 +10634,21 @@
       <c r="M79" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="N79" s="9"/>
-      <c r="O79" s="9"/>
-      <c r="P79" s="9"/>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vehicular mobility monitoring RS+DL (5th include; stop)</t>
+        </is>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
@@ -10741,101 +11385,101 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" display="10.1109/ITSC.2018.8569552"/>
-    <hyperlink ref="L3" r:id="rId2" display="10.1109/TCSVT.2022.3168279"/>
-    <hyperlink ref="L4" r:id="rId3" display="10.1109/JPROC.2022.3173031"/>
-    <hyperlink ref="L5" r:id="rId4" display="10.1109/MCOM.2017.1600238CM"/>
-    <hyperlink ref="L6" r:id="rId5" display="10.1109/TITS.2023.3275741"/>
-    <hyperlink ref="L7" r:id="rId6" display="10.1016/j.tra.2020.09.018"/>
-    <hyperlink ref="L8" r:id="rId7" display="10.1109/IV47402.2020.9304839"/>
-    <hyperlink ref="L9" r:id="rId8" display="10.1109/TITS.2020.3041746"/>
-    <hyperlink ref="L10" r:id="rId9" display="10.1016/j.trc.2019.11.023"/>
-    <hyperlink ref="L11" r:id="rId10" display="10.1007/s10489-021-02893-3"/>
-    <hyperlink ref="L12" r:id="rId11" display="10.1109/TNNLS.2021.3080276"/>
-    <hyperlink ref="L13" r:id="rId12" display="10.1109/TITS.2020.2983835"/>
-    <hyperlink ref="L14" r:id="rId13" display="10.1109/ACCESS.2022.3177904"/>
-    <hyperlink ref="L15" r:id="rId14" display="10.1109/TITS.2020.3003782"/>
-    <hyperlink ref="L16" r:id="rId15" display="10.1109/UVS.2019.8658300"/>
-    <hyperlink ref="L17" r:id="rId16" display="10.1016/j.comcom.2020.04.049"/>
-    <hyperlink ref="L18" r:id="rId17" display="10.1109/TVT.2022.3188769"/>
-    <hyperlink ref="L19" r:id="rId18" display="10.1109/TITS.2018.2797697"/>
-    <hyperlink ref="L20" r:id="rId19" display="10.1109/IV51971.2022.9827305"/>
-    <hyperlink ref="L21" r:id="rId20" display="10.1016/j.cose.2019.05.006"/>
-    <hyperlink ref="L22" r:id="rId21" display="10.1109/ITSC45102.2020.9294728"/>
-    <hyperlink ref="L23" r:id="rId22" display="10.1109/ACCESS.2020.2987622"/>
-    <hyperlink ref="L24" r:id="rId23" display="10.1109/ACCESS.2022.3149054"/>
-    <hyperlink ref="L25" r:id="rId24" display="10.1109/TITS.2021.3122567"/>
-    <hyperlink ref="L26" r:id="rId25" display="10.1109/TITS.2020.3040557"/>
-    <hyperlink ref="L27" r:id="rId26" display="10.1016/j.eswa.2023.120845"/>
-    <hyperlink ref="L28" r:id="rId27" display="10.1109/ICRA40945.2020.9196845"/>
-    <hyperlink ref="L29" r:id="rId28" display="10.1109/TVT.2020.3023861"/>
-    <hyperlink ref="L30" r:id="rId29" display="10.1016/j.physa.2023.128980"/>
-    <hyperlink ref="L31" r:id="rId30" display="10.1109/MWC.2018.1800155"/>
-    <hyperlink ref="L32" r:id="rId31" display="10.1016/j.ejor.2023.02.031"/>
-    <hyperlink ref="L33" r:id="rId32" display="10.1109/TII.2021.3101651"/>
-    <hyperlink ref="L34" r:id="rId33" display="10.1109/TITS.2020.3020220"/>
-    <hyperlink ref="L35" r:id="rId34" display="10.1109/TITS.2023.3252082"/>
-    <hyperlink ref="L36" r:id="rId35" display="10.1016/j.aap.2018.12.013"/>
-    <hyperlink ref="L37" r:id="rId36" display="10.1002/net.21847"/>
-    <hyperlink ref="L38" r:id="rId37" display="10.1109/ITSC55140.2022.9921959"/>
-    <hyperlink ref="L39" r:id="rId38" display="10.1016/j.comcom.2023.04.032"/>
-    <hyperlink ref="L40" r:id="rId39" display="10.3390/rs15153778"/>
-    <hyperlink ref="L41" r:id="rId40" display="10.1109/JIOT.2021.3103391"/>
-    <hyperlink ref="L42" r:id="rId41" display="10.1016/j.measurement.2023.113252"/>
-    <hyperlink ref="L43" r:id="rId42" display="10.3390/rs14143498"/>
-    <hyperlink ref="L44" r:id="rId43" display="10.1007/s11042-021-11146-x"/>
-    <hyperlink ref="L45" r:id="rId44" display="10.1109/WCNC.2018.8377077"/>
-    <hyperlink ref="L46" r:id="rId45" display="10.1016/j.patcog.2022.109019"/>
-    <hyperlink ref="L47" r:id="rId46" display="10.1016/j.comcom.2020.07.035"/>
-    <hyperlink ref="L48" r:id="rId47" display="10.1109/TITS.2022.3157394"/>
-    <hyperlink ref="L49" r:id="rId48" display="10.1109/TVT.2019.2898477"/>
-    <hyperlink ref="L50" r:id="rId49" display="10.1109/MNET.2018.1700286"/>
-    <hyperlink ref="L51" r:id="rId50" display="10.3390/rs13204027"/>
-    <hyperlink ref="L52" r:id="rId51" display="10.1109/TVT.2020.2981959"/>
-    <hyperlink ref="L53" r:id="rId52" display="10.1016/j.tre.2022.102816"/>
-    <hyperlink ref="L54" r:id="rId53" display="10.1109/ACCESS.2021.3058986"/>
-    <hyperlink ref="L55" r:id="rId54" display="10.3390/s21206905"/>
-    <hyperlink ref="L56" r:id="rId55" display="10.1109/CVPR42600.2020.00443"/>
-    <hyperlink ref="L57" r:id="rId56" display="10.1109/TGRS.2018.2841808"/>
-    <hyperlink ref="L58" r:id="rId57" display="10.1109/TAES.2021.3053115"/>
-    <hyperlink ref="L59" r:id="rId58" display="10.3390/rs13040573"/>
-    <hyperlink ref="L60" r:id="rId59" display="10.1109/ACCESS.2020.3026192"/>
-    <hyperlink ref="L61" r:id="rId60" display="10.1109/ACCESS.2020.2989790"/>
-    <hyperlink ref="L62" r:id="rId61" display="10.1109/TII.2017.2783439"/>
-    <hyperlink ref="L63" r:id="rId62" display="10.1016/j.aap.2021.106543"/>
-    <hyperlink ref="L64" r:id="rId63" display="10.1016/j.trc.2021.103506"/>
-    <hyperlink ref="L65" r:id="rId64" display="10.1109/TII.2022.3192675"/>
-    <hyperlink ref="L66" r:id="rId65" display="10.1016/j.compeleceng.2021.107372"/>
-    <hyperlink ref="L67" r:id="rId66" display="10.1016/j.aap.2017.10.015"/>
-    <hyperlink ref="L68" r:id="rId67" display="10.3390/en16062617"/>
-    <hyperlink ref="L69" r:id="rId68" display="10.1016/j.jairtraman.2020.101862"/>
-    <hyperlink ref="L70" r:id="rId69" display="10.1109/TNSE.2020.3043262"/>
-    <hyperlink ref="L71" r:id="rId70" display="10.1016/j.cie.2019.106118"/>
-    <hyperlink ref="L72" r:id="rId71" display="10.1109/COMST.2023.3312221"/>
-    <hyperlink ref="L73" r:id="rId72" display="10.1177/03611981231185768"/>
-    <hyperlink ref="L74" r:id="rId73" display="10.1016/j.asoc.2024.112015"/>
-    <hyperlink ref="L75" r:id="rId74" display="10.1109/TIV.2024.3414140"/>
-    <hyperlink ref="L76" r:id="rId75" display="10.3390/drones8030084"/>
-    <hyperlink ref="L77" r:id="rId76" display="10.1109/COMST.2024.3400121"/>
-    <hyperlink ref="L78" r:id="rId77" display="10.1016/j.dsp.2024.104594"/>
-    <hyperlink ref="L79" r:id="rId78" display="10.1016/j.measurement.2024.116579"/>
-    <hyperlink ref="L80" r:id="rId79" display="10.1016/j.compeleceng.2025.110313"/>
-    <hyperlink ref="L81" r:id="rId80" display="10.1109/TITS.2024.3445088"/>
-    <hyperlink ref="L82" r:id="rId81" display="10.1609/aaai.v38i9.28900"/>
-    <hyperlink ref="L83" r:id="rId82" display="10.1109/TITS.2024.3360251"/>
-    <hyperlink ref="L84" r:id="rId83" display="10.1016/j.jnca.2025.104134"/>
-    <hyperlink ref="L85" r:id="rId84" display="10.3390/drones9010054"/>
-    <hyperlink ref="L86" r:id="rId85" display="10.1109/TGRS.2024.3452550"/>
-    <hyperlink ref="L87" r:id="rId86" display="10.3390/rs17203414"/>
-    <hyperlink ref="L88" r:id="rId87" display="10.3390/drones9040248"/>
-    <hyperlink ref="L89" r:id="rId88" display="10.1109/TITS.2024.3358010"/>
-    <hyperlink ref="L90" r:id="rId89" display="10.1016/j.swevo.2025.101858"/>
-    <hyperlink ref="L91" r:id="rId90" display="10.3389/fnbot.2025.1681341"/>
-    <hyperlink ref="L92" r:id="rId91" display="10.1109/TCSVT.2024.3376399"/>
-    <hyperlink ref="L93" r:id="rId92" display="10.1007/s40747-025-02126-x"/>
-    <hyperlink ref="L94" r:id="rId93" display="10.1109/TITS.2024.3422039"/>
-    <hyperlink ref="L95" r:id="rId94" display="10.1109/TITS.2024.3437770"/>
-    <hyperlink ref="L96" r:id="rId95" display="10.1016/j.trc.2024.104615"/>
+    <hyperlink ref="L2" ns1:id="rId1" display="10.1109/ITSC.2018.8569552"/>
+    <hyperlink ref="L3" ns1:id="rId2" display="10.1109/TCSVT.2022.3168279"/>
+    <hyperlink ref="L4" ns1:id="rId3" display="10.1109/JPROC.2022.3173031"/>
+    <hyperlink ref="L5" ns1:id="rId4" display="10.1109/MCOM.2017.1600238CM"/>
+    <hyperlink ref="L6" ns1:id="rId5" display="10.1109/TITS.2023.3275741"/>
+    <hyperlink ref="L7" ns1:id="rId6" display="10.1016/j.tra.2020.09.018"/>
+    <hyperlink ref="L8" ns1:id="rId7" display="10.1109/IV47402.2020.9304839"/>
+    <hyperlink ref="L9" ns1:id="rId8" display="10.1109/TITS.2020.3041746"/>
+    <hyperlink ref="L10" ns1:id="rId9" display="10.1016/j.trc.2019.11.023"/>
+    <hyperlink ref="L11" ns1:id="rId10" display="10.1007/s10489-021-02893-3"/>
+    <hyperlink ref="L12" ns1:id="rId11" display="10.1109/TNNLS.2021.3080276"/>
+    <hyperlink ref="L13" ns1:id="rId12" display="10.1109/TITS.2020.2983835"/>
+    <hyperlink ref="L14" ns1:id="rId13" display="10.1109/ACCESS.2022.3177904"/>
+    <hyperlink ref="L15" ns1:id="rId14" display="10.1109/TITS.2020.3003782"/>
+    <hyperlink ref="L16" ns1:id="rId15" display="10.1109/UVS.2019.8658300"/>
+    <hyperlink ref="L17" ns1:id="rId16" display="10.1016/j.comcom.2020.04.049"/>
+    <hyperlink ref="L18" ns1:id="rId17" display="10.1109/TVT.2022.3188769"/>
+    <hyperlink ref="L19" ns1:id="rId18" display="10.1109/TITS.2018.2797697"/>
+    <hyperlink ref="L20" ns1:id="rId19" display="10.1109/IV51971.2022.9827305"/>
+    <hyperlink ref="L21" ns1:id="rId20" display="10.1016/j.cose.2019.05.006"/>
+    <hyperlink ref="L22" ns1:id="rId21" display="10.1109/ITSC45102.2020.9294728"/>
+    <hyperlink ref="L23" ns1:id="rId22" display="10.1109/ACCESS.2020.2987622"/>
+    <hyperlink ref="L24" ns1:id="rId23" display="10.1109/ACCESS.2022.3149054"/>
+    <hyperlink ref="L25" ns1:id="rId24" display="10.1109/TITS.2021.3122567"/>
+    <hyperlink ref="L26" ns1:id="rId25" display="10.1109/TITS.2020.3040557"/>
+    <hyperlink ref="L27" ns1:id="rId26" display="10.1016/j.eswa.2023.120845"/>
+    <hyperlink ref="L28" ns1:id="rId27" display="10.1109/ICRA40945.2020.9196845"/>
+    <hyperlink ref="L29" ns1:id="rId28" display="10.1109/TVT.2020.3023861"/>
+    <hyperlink ref="L30" ns1:id="rId29" display="10.1016/j.physa.2023.128980"/>
+    <hyperlink ref="L31" ns1:id="rId30" display="10.1109/MWC.2018.1800155"/>
+    <hyperlink ref="L32" ns1:id="rId31" display="10.1016/j.ejor.2023.02.031"/>
+    <hyperlink ref="L33" ns1:id="rId32" display="10.1109/TII.2021.3101651"/>
+    <hyperlink ref="L34" ns1:id="rId33" display="10.1109/TITS.2020.3020220"/>
+    <hyperlink ref="L35" ns1:id="rId34" display="10.1109/TITS.2023.3252082"/>
+    <hyperlink ref="L36" ns1:id="rId35" display="10.1016/j.aap.2018.12.013"/>
+    <hyperlink ref="L37" ns1:id="rId36" display="10.1002/net.21847"/>
+    <hyperlink ref="L38" ns1:id="rId37" display="10.1109/ITSC55140.2022.9921959"/>
+    <hyperlink ref="L39" ns1:id="rId38" display="10.1016/j.comcom.2023.04.032"/>
+    <hyperlink ref="L40" ns1:id="rId39" display="10.3390/rs15153778"/>
+    <hyperlink ref="L41" ns1:id="rId40" display="10.1109/JIOT.2021.3103391"/>
+    <hyperlink ref="L42" ns1:id="rId41" display="10.1016/j.measurement.2023.113252"/>
+    <hyperlink ref="L43" ns1:id="rId42" display="10.3390/rs14143498"/>
+    <hyperlink ref="L44" ns1:id="rId43" display="10.1007/s11042-021-11146-x"/>
+    <hyperlink ref="L45" ns1:id="rId44" display="10.1109/WCNC.2018.8377077"/>
+    <hyperlink ref="L46" ns1:id="rId45" display="10.1016/j.patcog.2022.109019"/>
+    <hyperlink ref="L47" ns1:id="rId46" display="10.1016/j.comcom.2020.07.035"/>
+    <hyperlink ref="L48" ns1:id="rId47" display="10.1109/TITS.2022.3157394"/>
+    <hyperlink ref="L49" ns1:id="rId48" display="10.1109/TVT.2019.2898477"/>
+    <hyperlink ref="L50" ns1:id="rId49" display="10.1109/MNET.2018.1700286"/>
+    <hyperlink ref="L51" ns1:id="rId50" display="10.3390/rs13204027"/>
+    <hyperlink ref="L52" ns1:id="rId51" display="10.1109/TVT.2020.2981959"/>
+    <hyperlink ref="L53" ns1:id="rId52" display="10.1016/j.tre.2022.102816"/>
+    <hyperlink ref="L54" ns1:id="rId53" display="10.1109/ACCESS.2021.3058986"/>
+    <hyperlink ref="L55" ns1:id="rId54" display="10.3390/s21206905"/>
+    <hyperlink ref="L56" ns1:id="rId55" display="10.1109/CVPR42600.2020.00443"/>
+    <hyperlink ref="L57" ns1:id="rId56" display="10.1109/TGRS.2018.2841808"/>
+    <hyperlink ref="L58" ns1:id="rId57" display="10.1109/TAES.2021.3053115"/>
+    <hyperlink ref="L59" ns1:id="rId58" display="10.3390/rs13040573"/>
+    <hyperlink ref="L60" ns1:id="rId59" display="10.1109/ACCESS.2020.3026192"/>
+    <hyperlink ref="L61" ns1:id="rId60" display="10.1109/ACCESS.2020.2989790"/>
+    <hyperlink ref="L62" ns1:id="rId61" display="10.1109/TII.2017.2783439"/>
+    <hyperlink ref="L63" ns1:id="rId62" display="10.1016/j.aap.2021.106543"/>
+    <hyperlink ref="L64" ns1:id="rId63" display="10.1016/j.trc.2021.103506"/>
+    <hyperlink ref="L65" ns1:id="rId64" display="10.1109/TII.2022.3192675"/>
+    <hyperlink ref="L66" ns1:id="rId65" display="10.1016/j.compeleceng.2021.107372"/>
+    <hyperlink ref="L67" ns1:id="rId66" display="10.1016/j.aap.2017.10.015"/>
+    <hyperlink ref="L68" ns1:id="rId67" display="10.3390/en16062617"/>
+    <hyperlink ref="L69" ns1:id="rId68" display="10.1016/j.jairtraman.2020.101862"/>
+    <hyperlink ref="L70" ns1:id="rId69" display="10.1109/TNSE.2020.3043262"/>
+    <hyperlink ref="L71" ns1:id="rId70" display="10.1016/j.cie.2019.106118"/>
+    <hyperlink ref="L72" ns1:id="rId71" display="10.1109/COMST.2023.3312221"/>
+    <hyperlink ref="L73" ns1:id="rId72" display="10.1177/03611981231185768"/>
+    <hyperlink ref="L74" ns1:id="rId73" display="10.1016/j.asoc.2024.112015"/>
+    <hyperlink ref="L75" ns1:id="rId74" display="10.1109/TIV.2024.3414140"/>
+    <hyperlink ref="L76" ns1:id="rId75" display="10.3390/drones8030084"/>
+    <hyperlink ref="L77" ns1:id="rId76" display="10.1109/COMST.2024.3400121"/>
+    <hyperlink ref="L78" ns1:id="rId77" display="10.1016/j.dsp.2024.104594"/>
+    <hyperlink ref="L79" ns1:id="rId78" display="10.1016/j.measurement.2024.116579"/>
+    <hyperlink ref="L80" ns1:id="rId79" display="10.1016/j.compeleceng.2025.110313"/>
+    <hyperlink ref="L81" ns1:id="rId80" display="10.1109/TITS.2024.3445088"/>
+    <hyperlink ref="L82" ns1:id="rId81" display="10.1609/aaai.v38i9.28900"/>
+    <hyperlink ref="L83" ns1:id="rId82" display="10.1109/TITS.2024.3360251"/>
+    <hyperlink ref="L84" ns1:id="rId83" display="10.1016/j.jnca.2025.104134"/>
+    <hyperlink ref="L85" ns1:id="rId84" display="10.3390/drones9010054"/>
+    <hyperlink ref="L86" ns1:id="rId85" display="10.1109/TGRS.2024.3452550"/>
+    <hyperlink ref="L87" ns1:id="rId86" display="10.3390/rs17203414"/>
+    <hyperlink ref="L88" ns1:id="rId87" display="10.3390/drones9040248"/>
+    <hyperlink ref="L89" ns1:id="rId88" display="10.1109/TITS.2024.3358010"/>
+    <hyperlink ref="L90" ns1:id="rId89" display="10.1016/j.swevo.2025.101858"/>
+    <hyperlink ref="L91" ns1:id="rId90" display="10.3389/fnbot.2025.1681341"/>
+    <hyperlink ref="L92" ns1:id="rId91" display="10.1109/TCSVT.2024.3376399"/>
+    <hyperlink ref="L93" ns1:id="rId92" display="10.1007/s40747-025-02126-x"/>
+    <hyperlink ref="L94" ns1:id="rId93" display="10.1109/TITS.2024.3422039"/>
+    <hyperlink ref="L95" ns1:id="rId94" display="10.1109/TITS.2024.3437770"/>
+    <hyperlink ref="L96" ns1:id="rId95" display="10.1016/j.trc.2024.104615"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10844,12 +11488,12 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId96"/>
+  <drawing ns1:id="rId96"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -10958,9 +11602,21 @@
       <c r="M2" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generic DNN verifier (Reluplex)</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
@@ -11000,9 +11656,21 @@
       <c r="M3" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAM history/market overview (interview study)</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -11042,9 +11710,21 @@
       <c r="M4" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-UAV; security/privacy purpose</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
@@ -11084,9 +11764,21 @@
       <c r="M5" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV detection, no stated purpose</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
@@ -11128,9 +11820,21 @@
       <c r="M6" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-drone systems survey</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
@@ -11168,9 +11872,21 @@
       <c r="M7" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAM airspace integration (traffic mgmt)</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
@@ -11210,9 +11926,21 @@
       <c r="M8" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collision-avoidance review</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -11250,9 +11978,21 @@
       <c r="M9" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-drone surveillance system</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
@@ -11294,9 +12034,21 @@
       <c r="M10" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone-detection ML review</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
@@ -11338,9 +12090,21 @@
       <c r="M11" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unauthorized-drone detection review</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
@@ -11380,9 +12144,21 @@
       <c r="M12" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internet of Drones: low-altitude ATM architecture</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
@@ -11422,9 +12198,21 @@
       <c r="M13" s="7" t="s">
         <v>638</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone detection/ID, security</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
@@ -11464,9 +12252,21 @@
       <c r="M14" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air-to-air detection, see-and-avoid</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
@@ -11502,9 +12302,21 @@
       <c r="M15" s="7" t="s">
         <v>648</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM Concept of Operations</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
@@ -11544,9 +12356,21 @@
       <c r="M16" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-fingerprint UAV detection, surveillance</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
@@ -11586,9 +12410,21 @@
       <c r="M17" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amateur-drone acoustic detection, security</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
@@ -11628,9 +12464,21 @@
       <c r="M18" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone detection, security</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
@@ -11670,9 +12518,21 @@
       <c r="M19" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection for security</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
@@ -11714,9 +12574,21 @@
       <c r="M20" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Systematic literature review (drone control)</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
@@ -11756,9 +12628,21 @@
       <c r="M21" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radar UAV detection, prevent unauthorized flying</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
@@ -11798,9 +12682,21 @@
       <c r="M22" s="7" t="s">
         <v>687</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, drone-protection systems</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
@@ -11840,9 +12736,21 @@
       <c r="M23" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JRC comms/radar resource allocation</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="n">
@@ -11882,9 +12790,21 @@
       <c r="M24" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U-space Concept of Operations</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="n">
@@ -11922,9 +12842,21 @@
       <c r="M25" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF-fingerprint micro-UAV detection</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="n">
@@ -11964,9 +12896,21 @@
       <c r="M26" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, no traffic purpose</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="n">
@@ -12006,9 +12950,21 @@
       <c r="M27" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
+      <c r="N27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acoustic drone detection, safety/privacy</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="n">
@@ -12048,9 +13004,21 @@
       <c r="M28" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone-vs-bird counter-drone challenge</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="n">
@@ -12090,9 +13058,21 @@
       <c r="M29" s="7" t="s">
         <v>726</v>
       </c>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
+      <c r="N29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DRL detect-and-avoid / BVLOS collision avoidance</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="n">
@@ -12130,9 +13110,21 @@
       <c r="M30" s="7" t="s">
         <v>731</v>
       </c>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-drone multi-sensor detection</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="n">
@@ -12172,9 +13164,21 @@
       <c r="M31" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unauthorized-UAV detection/mitigation</t>
+        </is>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="n">
@@ -12216,9 +13220,21 @@
       <c r="M32" s="7" t="s">
         <v>742</v>
       </c>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Path-planning/obstacle-avoidance survey</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="n">
@@ -12256,9 +13272,21 @@
       <c r="M33" s="7" t="s">
         <v>747</v>
       </c>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-rotor CFD aerodynamics</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="n">
@@ -12298,9 +13326,21 @@
       <c r="M34" s="7" t="s">
         <v>753</v>
       </c>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone detection, security</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="n">
@@ -12340,9 +13380,21 @@
       <c r="M35" s="7" t="s">
         <v>758</v>
       </c>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
+      <c r="N35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unsure</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6G UTM "A Perspective"; include if background counts (borderline E3/S)</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="n">
@@ -12382,9 +13434,21 @@
       <c r="M36" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, unauthorized/security</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="n">
@@ -12424,9 +13488,21 @@
       <c r="M37" s="7" t="s">
         <v>768</v>
       </c>
-      <c r="N37" s="9"/>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relay-comms planning for swarm</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="n">
@@ -12466,9 +13542,21 @@
       <c r="M38" s="7" t="s">
         <v>773</v>
       </c>
-      <c r="N38" s="9"/>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
+      <c r="N38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WiFi/RF-fingerprint UAV detection, security</t>
+        </is>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="n">
@@ -12508,9 +13596,21 @@
       <c r="M39" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
+      <c r="N39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-UAV IR detection (restricted areas/airports)</t>
+        </is>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="n">
@@ -12550,9 +13650,21 @@
       <c r="M40" s="7" t="s">
         <v>783</v>
       </c>
-      <c r="N40" s="9"/>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV-LEO edge-computing offloading</t>
+        </is>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="n">
@@ -12592,9 +13704,21 @@
       <c r="M41" s="7" t="s">
         <v>788</v>
       </c>
-      <c r="N41" s="9"/>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
+      <c r="N41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF UAV detection, illegitimate use</t>
+        </is>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="n">
@@ -12634,9 +13758,21 @@
       <c r="M42" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
+      <c r="N42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acoustic amateur-drone surveillance</t>
+        </is>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="n">
@@ -12676,9 +13812,21 @@
       <c r="M43" s="7" t="s">
         <v>798</v>
       </c>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="N43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autonomous flight-path trajectory optimisation (airspace)</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="n">
@@ -12718,9 +13866,21 @@
       <c r="M44" s="7" t="s">
         <v>804</v>
       </c>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
+      <c r="N44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-UAV IR detection (airports)</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="n">
@@ -12760,9 +13920,21 @@
       <c r="M45" s="7" t="s">
         <v>809</v>
       </c>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
+      <c r="N45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gust/turbulence modelling near buildings</t>
+        </is>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="n">
@@ -12802,9 +13974,21 @@
       <c r="M46" s="7" t="s">
         <v>814</v>
       </c>
-      <c r="N46" s="9"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
+      <c r="N46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C-UAS RF-ID drone detection/tracking</t>
+        </is>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="n">
@@ -12844,9 +14028,21 @@
       <c r="M47" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="N47" s="9"/>
-      <c r="O47" s="9"/>
-      <c r="P47" s="9"/>
+      <c r="N47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, security/surveillance</t>
+        </is>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="n">
@@ -12886,9 +14082,21 @@
       <c r="M48" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="N48" s="9"/>
-      <c r="O48" s="9"/>
-      <c r="P48" s="9"/>
+      <c r="N48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF fingerprinting UAVs, anti-spoof ID</t>
+        </is>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="n">
@@ -12926,9 +14134,21 @@
       <c r="M49" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="N49" s="9"/>
-      <c r="O49" s="9"/>
-      <c r="P49" s="9"/>
+      <c r="N49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Li-ion battery prognosis</t>
+        </is>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="n">
@@ -12968,9 +14188,21 @@
       <c r="M50" s="7" t="s">
         <v>835</v>
       </c>
-      <c r="N50" s="9"/>
-      <c r="O50" s="9"/>
-      <c r="P50" s="9"/>
+      <c r="N50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audio drone detection, malicious use</t>
+        </is>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="n">
@@ -13010,9 +14242,21 @@
       <c r="M51" s="7" t="s">
         <v>841</v>
       </c>
-      <c r="N51" s="9"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E2</t>
+        </is>
+      </c>
+      <c r="P51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unmanned GROUND vehicle; no UAV role</t>
+        </is>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="n">
@@ -13052,9 +14296,21 @@
       <c r="M52" s="7" t="s">
         <v>847</v>
       </c>
-      <c r="N52" s="9"/>
-      <c r="O52" s="9"/>
-      <c r="P52" s="9"/>
+      <c r="N52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-UAV IR small-target detection</t>
+        </is>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="n">
@@ -13094,9 +14350,21 @@
       <c r="M53" s="7" t="s">
         <v>853</v>
       </c>
-      <c r="N53" s="9"/>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9"/>
+      <c r="N53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV-to-UAV detection/tracking, see-and-avoid</t>
+        </is>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="n">
@@ -13136,9 +14404,21 @@
       <c r="M54" s="7" t="s">
         <v>859</v>
       </c>
-      <c r="N54" s="9"/>
-      <c r="O54" s="9"/>
-      <c r="P54" s="9"/>
+      <c r="N54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review of autonomous navigation systems for UAS</t>
+        </is>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="n">
@@ -13178,9 +14458,21 @@
       <c r="M55" s="7" t="s">
         <v>865</v>
       </c>
-      <c r="N55" s="9"/>
-      <c r="O55" s="9"/>
-      <c r="P55" s="9"/>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audio drone detection, malicious/security</t>
+        </is>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="n">
@@ -13220,9 +14512,21 @@
       <c r="M56" s="7" t="s">
         <v>871</v>
       </c>
-      <c r="N56" s="9"/>
-      <c r="O56" s="9"/>
-      <c r="P56" s="9"/>
+      <c r="N56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decentralized multi-UAV task allocation (fleet coord)</t>
+        </is>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="n">
@@ -13262,9 +14566,21 @@
       <c r="M57" s="7" t="s">
         <v>877</v>
       </c>
-      <c r="N57" s="9"/>
-      <c r="O57" s="9"/>
-      <c r="P57" s="9"/>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF UAV detection/ID, security</t>
+        </is>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="n">
@@ -13304,9 +14620,21 @@
       <c r="M58" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="N58" s="9"/>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decentralized MAPF for UTM (conflict resolution)</t>
+        </is>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="n">
@@ -13346,9 +14674,21 @@
       <c r="M59" s="7" t="s">
         <v>887</v>
       </c>
-      <c r="N59" s="9"/>
-      <c r="O59" s="9"/>
-      <c r="P59" s="9"/>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Micro-Doppler SUAV detection, security</t>
+        </is>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="n">
@@ -13386,9 +14726,21 @@
       <c r="M60" s="7" t="s">
         <v>892</v>
       </c>
-      <c r="N60" s="9"/>
-      <c r="O60" s="9"/>
-      <c r="P60" s="9"/>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AED drone DELIVERY (emergency-response but delivery mechanism)</t>
+        </is>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="n">
@@ -13426,9 +14778,21 @@
       <c r="M61" s="7" t="s">
         <v>897</v>
       </c>
-      <c r="N61" s="9"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="9"/>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, no purpose stated</t>
+        </is>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="n">
@@ -13466,9 +14830,21 @@
       <c r="M62" s="7" t="s">
         <v>902</v>
       </c>
-      <c r="N62" s="9"/>
-      <c r="O62" s="9"/>
-      <c r="P62" s="9"/>
+      <c r="N62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACAS X collision avoidance for manned+unmanned aircraft</t>
+        </is>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="n">
@@ -13508,9 +14884,21 @@
       <c r="M63" s="7" t="s">
         <v>908</v>
       </c>
-      <c r="N63" s="9"/>
-      <c r="O63" s="9"/>
-      <c r="P63" s="9"/>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GPS-spoofing detection (traffic-system security/hazard)</t>
+        </is>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="n">
@@ -13550,9 +14938,21 @@
       <c r="M64" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="N64" s="9"/>
-      <c r="O64" s="9"/>
-      <c r="P64" s="9"/>
+      <c r="N64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wind-aware path planning, UAM airspace</t>
+        </is>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="n">
@@ -13592,9 +14992,21 @@
       <c r="M65" s="7" t="s">
         <v>919</v>
       </c>
-      <c r="N65" s="9"/>
-      <c r="O65" s="9"/>
-      <c r="P65" s="9"/>
+      <c r="N65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-drone real-time detection, high-security areas</t>
+        </is>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="n">
@@ -13634,9 +15046,21 @@
       <c r="M66" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="N66" s="9"/>
-      <c r="O66" s="9"/>
-      <c r="P66" s="9"/>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-drone multi-sensor detection</t>
+        </is>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="n">
@@ -13674,9 +15098,21 @@
       <c r="M67" s="7" t="s">
         <v>929</v>
       </c>
-      <c r="N67" s="9"/>
-      <c r="O67" s="9"/>
-      <c r="P67" s="9"/>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radar micro-UAV detection, no traffic purpose</t>
+        </is>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="n">
@@ -13716,9 +15152,21 @@
       <c r="M68" s="7" t="s">
         <v>934</v>
       </c>
-      <c r="N68" s="9"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="9"/>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O68" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P68" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swarm 4D path planning + conflict resolution (AirMatrix)</t>
+        </is>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="n">
@@ -13758,9 +15206,21 @@
       <c r="M69" s="7" t="s">
         <v>940</v>
       </c>
-      <c r="N69" s="9"/>
-      <c r="O69" s="9"/>
-      <c r="P69" s="9"/>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-drone RF detection</t>
+        </is>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="n">
@@ -13800,9 +15260,21 @@
       <c r="M70" s="7" t="s">
         <v>946</v>
       </c>
-      <c r="N70" s="9"/>
-      <c r="O70" s="9"/>
-      <c r="P70" s="9"/>
+      <c r="N70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Authentication framework (IoD)</t>
+        </is>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="n">
@@ -13840,9 +15312,21 @@
       <c r="M71" s="7" t="s">
         <v>951</v>
       </c>
-      <c r="N71" s="9"/>
-      <c r="O71" s="9"/>
-      <c r="P71" s="9"/>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acoustic drone detection, illegal activities</t>
+        </is>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="n">
@@ -13882,9 +15366,21 @@
       <c r="M72" s="7" t="s">
         <v>956</v>
       </c>
-      <c r="N72" s="9"/>
-      <c r="O72" s="9"/>
-      <c r="P72" s="9"/>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone classification, security</t>
+        </is>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
@@ -13924,9 +15420,21 @@
       <c r="M73" s="7" t="s">
         <v>961</v>
       </c>
-      <c r="N73" s="9"/>
-      <c r="O73" s="9"/>
-      <c r="P73" s="9"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, security threats</t>
+        </is>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
@@ -13966,9 +15474,21 @@
       <c r="M74" s="7" t="s">
         <v>966</v>
       </c>
-      <c r="N74" s="9"/>
-      <c r="O74" s="9"/>
-      <c r="P74" s="9"/>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WiFi drone surveillance, security</t>
+        </is>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
@@ -14006,9 +15526,21 @@
       <c r="M75" s="7" t="s">
         <v>971</v>
       </c>
-      <c r="N75" s="9"/>
-      <c r="O75" s="9"/>
-      <c r="P75" s="9"/>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone-vs-bird detection challenge</t>
+        </is>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
@@ -14048,9 +15580,21 @@
       <c r="M76" s="7" t="s">
         <v>976</v>
       </c>
-      <c r="N76" s="9"/>
-      <c r="O76" s="9"/>
-      <c r="P76" s="9"/>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone detection, security/privacy</t>
+        </is>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
@@ -14090,9 +15634,21 @@
       <c r="M77" s="7" t="s">
         <v>981</v>
       </c>
-      <c r="N77" s="9"/>
-      <c r="O77" s="9"/>
-      <c r="P77" s="9"/>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sensor-fusion drone detection, no purpose</t>
+        </is>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
@@ -14132,9 +15688,21 @@
       <c r="M78" s="7" t="s">
         <v>986</v>
       </c>
-      <c r="N78" s="9"/>
-      <c r="O78" s="9"/>
-      <c r="P78" s="9"/>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VTOL virtual-tube ATM (airway, inter-agent CA)</t>
+        </is>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="n">
@@ -14176,9 +15744,21 @@
       <c r="M79" s="7" t="s">
         <v>992</v>
       </c>
-      <c r="N79" s="9"/>
-      <c r="O79" s="9"/>
-      <c r="P79" s="9"/>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Systematic review of collision avoidance</t>
+        </is>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="n">
@@ -14218,9 +15798,21 @@
       <c r="M80" s="7" t="s">
         <v>997</v>
       </c>
-      <c r="N80" s="9"/>
-      <c r="O80" s="9"/>
-      <c r="P80" s="9"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P80" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, airport security</t>
+        </is>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="n">
@@ -14260,9 +15852,21 @@
       <c r="M81" s="7" t="s">
         <v>1002</v>
       </c>
-      <c r="N81" s="9"/>
-      <c r="O81" s="9"/>
-      <c r="P81" s="9"/>
+      <c r="N81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P81" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lidar drone detection, malicious use</t>
+        </is>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="n">
@@ -14300,9 +15904,21 @@
       <c r="M82" s="7" t="s">
         <v>1007</v>
       </c>
-      <c r="N82" s="9"/>
-      <c r="O82" s="9"/>
-      <c r="P82" s="9"/>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P82" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV visual detection, aerial security systems</t>
+        </is>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="n">
@@ -14340,9 +15956,21 @@
       <c r="M83" s="7" t="s">
         <v>1011</v>
       </c>
-      <c r="N83" s="9"/>
-      <c r="O83" s="9"/>
-      <c r="P83" s="9"/>
+      <c r="N83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unsure</t>
+        </is>
+      </c>
+      <c r="O83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P83" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone-from-drone detection; purpose stated as generic surroundings-awareness, not explicit DAA</t>
+        </is>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="n">
@@ -14382,9 +16010,21 @@
       <c r="M84" s="7" t="s">
         <v>1017</v>
       </c>
-      <c r="N84" s="9"/>
-      <c r="O84" s="9"/>
-      <c r="P84" s="9"/>
+      <c r="N84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-UAV object detection</t>
+        </is>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="n">
@@ -14424,9 +16064,21 @@
       <c r="M85" s="7" t="s">
         <v>1023</v>
       </c>
-      <c r="N85" s="9"/>
-      <c r="O85" s="9"/>
-      <c r="P85" s="9"/>
+      <c r="N85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autonomous flight-trajectory control, smart-city airspace</t>
+        </is>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="n">
@@ -14466,9 +16118,21 @@
       <c r="M86" s="7" t="s">
         <v>1029</v>
       </c>
-      <c r="N86" s="9"/>
-      <c r="O86" s="9"/>
-      <c r="P86" s="9"/>
+      <c r="N86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV icing / propeller ice protection</t>
+        </is>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="n">
@@ -14508,9 +16172,21 @@
       <c r="M87" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="N87" s="9"/>
-      <c r="O87" s="9"/>
-      <c r="P87" s="9"/>
+      <c r="N87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone detection, airfields/military</t>
+        </is>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="n">
@@ -14550,9 +16226,21 @@
       <c r="M88" s="7" t="s">
         <v>1039</v>
       </c>
-      <c r="N88" s="9"/>
-      <c r="O88" s="9"/>
-      <c r="P88" s="9"/>
+      <c r="N88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E3</t>
+        </is>
+      </c>
+      <c r="P88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAM weather-barriers assessment, no capability</t>
+        </is>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="n">
@@ -14592,9 +16280,21 @@
       <c r="M89" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="N89" s="9"/>
-      <c r="O89" s="9"/>
-      <c r="P89" s="9"/>
+      <c r="N89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV detection/localization, security threats</t>
+        </is>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="n">
@@ -14634,9 +16334,21 @@
       <c r="M90" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="N90" s="9"/>
-      <c r="O90" s="9"/>
-      <c r="P90" s="9"/>
+      <c r="N90" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O90" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P90" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone surveillance, amateur drones</t>
+        </is>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="n">
@@ -14676,9 +16388,21 @@
       <c r="M91" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="N91" s="9"/>
-      <c r="O91" s="9"/>
-      <c r="P91" s="9"/>
+      <c r="N91" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O91" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P91" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unauthorized-UAV detection, illicit use</t>
+        </is>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="n">
@@ -14718,9 +16442,21 @@
       <c r="M92" s="7" t="s">
         <v>1059</v>
       </c>
-      <c r="N92" s="9"/>
-      <c r="O92" s="9"/>
-      <c r="P92" s="9"/>
+      <c r="N92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P92" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooperative pursuit of unauthorized UAVs (counter-UAS)</t>
+        </is>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="n">
@@ -14760,9 +16496,21 @@
       <c r="M93" s="7" t="s">
         <v>1064</v>
       </c>
-      <c r="N93" s="9"/>
-      <c r="O93" s="9"/>
-      <c r="P93" s="9"/>
+      <c r="N93" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O93" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P93" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radar cross-section drone detection</t>
+        </is>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="n">
@@ -14800,9 +16548,21 @@
       <c r="M94" s="7" t="s">
         <v>1068</v>
       </c>
-      <c r="N94" s="9"/>
-      <c r="O94" s="9"/>
-      <c r="P94" s="9"/>
+      <c r="N94" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unsure</t>
+        </is>
+      </c>
+      <c r="O94" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P94" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Swarm LiDAR odometry/state estimation; fleet-coord-adjacent but core is localization</t>
+        </is>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="n">
@@ -14842,9 +16602,21 @@
       <c r="M95" s="7" t="s">
         <v>1073</v>
       </c>
-      <c r="N95" s="9"/>
-      <c r="O95" s="9"/>
-      <c r="P95" s="9"/>
+      <c r="N95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foggy drone detection (drone-as-target), no traffic purpose</t>
+        </is>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="n">
@@ -14882,9 +16654,21 @@
       <c r="M96" s="7" t="s">
         <v>1078</v>
       </c>
-      <c r="N96" s="9"/>
-      <c r="O96" s="9"/>
-      <c r="P96" s="9"/>
+      <c r="N96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3GPP UAS comms-standards survey</t>
+        </is>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="n">
@@ -14924,9 +16708,21 @@
       <c r="M97" s="7" t="s">
         <v>1084</v>
       </c>
-      <c r="N97" s="9"/>
-      <c r="O97" s="9"/>
-      <c r="P97" s="9"/>
+      <c r="N97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM via crowd-sensing/blockchain (airspace mgmt, remote ID)</t>
+        </is>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="n">
@@ -14966,9 +16762,21 @@
       <c r="M98" s="7" t="s">
         <v>1090</v>
       </c>
-      <c r="N98" s="9"/>
-      <c r="O98" s="9"/>
-      <c r="P98" s="9"/>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection, no purpose</t>
+        </is>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="n">
@@ -15008,9 +16816,21 @@
       <c r="M99" s="7" t="s">
         <v>1095</v>
       </c>
-      <c r="N99" s="9"/>
-      <c r="O99" s="9"/>
-      <c r="P99" s="9"/>
+      <c r="N99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAM traffic-demand analysis</t>
+        </is>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="n">
@@ -15050,9 +16870,21 @@
       <c r="M100" s="7" t="s">
         <v>1100</v>
       </c>
-      <c r="N100" s="9"/>
-      <c r="O100" s="9"/>
-      <c r="P100" s="9"/>
+      <c r="N100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-UAV IR surveillance</t>
+        </is>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="n">
@@ -15092,9 +16924,21 @@
       <c r="M101" s="7" t="s">
         <v>1105</v>
       </c>
-      <c r="N101" s="9"/>
-      <c r="O101" s="9"/>
-      <c r="P101" s="9"/>
+      <c r="N101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E3</t>
+        </is>
+      </c>
+      <c r="P101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAM societal-acceptance mitigations, no capability</t>
+        </is>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="n">
@@ -15134,9 +16978,21 @@
       <c r="M102" s="7" t="s">
         <v>1111</v>
       </c>
-      <c r="N102" s="9"/>
-      <c r="O102" s="9"/>
-      <c r="P102" s="9"/>
+      <c r="N102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LES turbulence/wind simulation</t>
+        </is>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="n">
@@ -15176,9 +17032,21 @@
       <c r="M103" s="7" t="s">
         <v>1116</v>
       </c>
-      <c r="N103" s="9"/>
-      <c r="O103" s="9"/>
-      <c r="P103" s="9"/>
+      <c r="N103" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O103" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P103" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-UAV 4D CD&amp;R / strategic deconfliction</t>
+        </is>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="n">
@@ -15218,9 +17086,21 @@
       <c r="M104" s="7" t="s">
         <v>1122</v>
       </c>
-      <c r="N104" s="9"/>
-      <c r="O104" s="9"/>
-      <c r="P104" s="9"/>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O104" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P104" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ML UAV detection over encrypted WiFi, forensics</t>
+        </is>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="n">
@@ -15260,9 +17140,21 @@
       <c r="M105" s="7" t="s">
         <v>1128</v>
       </c>
-      <c r="N105" s="9"/>
-      <c r="O105" s="9"/>
-      <c r="P105" s="9"/>
+      <c r="N105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RF drone classification</t>
+        </is>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="n">
@@ -15302,9 +17194,21 @@
       <c r="M106" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="N106" s="9"/>
-      <c r="O106" s="9"/>
-      <c r="P106" s="9"/>
+      <c r="N106" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O106" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P106" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audio-camera drone detection, security</t>
+        </is>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="n">
@@ -15344,9 +17248,21 @@
       <c r="M107" s="7" t="s">
         <v>1140</v>
       </c>
-      <c r="N107" s="9"/>
-      <c r="O107" s="9"/>
-      <c r="P107" s="9"/>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone detection surveillance, terrorism/smuggling</t>
+        </is>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="n">
@@ -15386,9 +17302,21 @@
       <c r="M108" s="7" t="s">
         <v>1145</v>
       </c>
-      <c r="N108" s="9"/>
-      <c r="O108" s="9"/>
-      <c r="P108" s="9"/>
+      <c r="N108" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O108" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P108" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compressed-RF UAV detection, misuse</t>
+        </is>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="n">
@@ -15430,9 +17358,21 @@
       <c r="M109" s="7" t="s">
         <v>1150</v>
       </c>
-      <c r="N109" s="9"/>
-      <c r="O109" s="9"/>
-      <c r="P109" s="9"/>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RNN drone-sound detection review</t>
+        </is>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="n">
@@ -15472,9 +17412,21 @@
       <c r="M110" s="7" t="s">
         <v>1156</v>
       </c>
-      <c r="N110" s="9"/>
-      <c r="O110" s="9"/>
-      <c r="P110" s="9"/>
+      <c r="N110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV traffic control via gNB-IoT 5G (20th include; stop)</t>
+        </is>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="n">
@@ -15556,9 +17508,21 @@
       <c r="M112" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="N112" s="9"/>
-      <c r="O112" s="9"/>
-      <c r="P112" s="9"/>
+      <c r="N112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAE networks architecture/overview</t>
+        </is>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="7" t="n">
@@ -15598,9 +17562,21 @@
       <c r="M113" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="N113" s="9"/>
-      <c r="O113" s="9"/>
-      <c r="P113" s="9"/>
+      <c r="N113" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O113" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P113" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAC beamforming/trajectory + unauthorized sensing</t>
+        </is>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="7" t="n">
@@ -15640,9 +17616,21 @@
       <c r="M114" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="N114" s="9"/>
-      <c r="O114" s="9"/>
-      <c r="P114" s="9"/>
+      <c r="N114" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unsure</t>
+        </is>
+      </c>
+      <c r="O114" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P114" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open-water SAR detection = maritime content in air pool (domain mismatch)</t>
+        </is>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="7" t="n">
@@ -15682,9 +17670,21 @@
       <c r="M115" s="7" t="s">
         <v>1182</v>
       </c>
-      <c r="N115" s="9"/>
-      <c r="O115" s="9"/>
-      <c r="P115" s="9"/>
+      <c r="N115" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O115" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P115" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low-altitude airspace management + UAV ops architecture</t>
+        </is>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="7" t="n">
@@ -15724,9 +17724,21 @@
       <c r="M116" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="N116" s="9"/>
-      <c r="O116" s="9"/>
-      <c r="P116" s="9"/>
+      <c r="N116" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O116" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P116" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anti-drone YOLOv8 detection</t>
+        </is>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="7" t="n">
@@ -15766,9 +17778,21 @@
       <c r="M117" s="7" t="s">
         <v>1192</v>
       </c>
-      <c r="N117" s="9"/>
-      <c r="O117" s="9"/>
-      <c r="P117" s="9"/>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P117" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small-drone detection, misuse/security</t>
+        </is>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="7" t="n">
@@ -15808,9 +17832,21 @@
       <c r="M118" s="7" t="s">
         <v>1197</v>
       </c>
-      <c r="N118" s="9"/>
-      <c r="O118" s="9"/>
-      <c r="P118" s="9"/>
+      <c r="N118" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O118" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P118" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VisDrone detection, drone surveillance/military</t>
+        </is>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="7" t="n">
@@ -15852,9 +17888,21 @@
       <c r="M119" s="7" t="s">
         <v>1202</v>
       </c>
-      <c r="N119" s="9"/>
-      <c r="O119" s="9"/>
-      <c r="P119" s="9"/>
+      <c r="N119" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O119" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P119" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CD&amp;R-in-UTM survey</t>
+        </is>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="7" t="n">
@@ -15896,9 +17944,21 @@
       <c r="M120" s="7" t="s">
         <v>1207</v>
       </c>
-      <c r="N120" s="9"/>
-      <c r="O120" s="9"/>
-      <c r="P120" s="9"/>
+      <c r="N120" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O120" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P120" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">State-of-UAM assessment/review</t>
+        </is>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="7" t="n">
@@ -15940,9 +18000,21 @@
       <c r="M121" s="7" t="s">
         <v>1213</v>
       </c>
-      <c r="N121" s="9"/>
-      <c r="O121" s="9"/>
-      <c r="P121" s="9"/>
+      <c r="N121" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O121" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P121" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM survey</t>
+        </is>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="7" t="n">
@@ -15982,9 +18054,21 @@
       <c r="M122" s="7" t="s">
         <v>1218</v>
       </c>
-      <c r="N122" s="9"/>
-      <c r="O122" s="9"/>
-      <c r="P122" s="9"/>
+      <c r="N122" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O122" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P122" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAV small-target detection, no traffic purpose</t>
+        </is>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="7" t="n">
@@ -16024,9 +18108,21 @@
       <c r="M123" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="N123" s="9"/>
-      <c r="O123" s="9"/>
-      <c r="P123" s="9"/>
+      <c r="N123" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O123" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P123" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAC resource allocation + unauthorized localization</t>
+        </is>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="7" t="n">
@@ -16066,9 +18162,21 @@
       <c r="M124" s="7" t="s">
         <v>1228</v>
       </c>
-      <c r="N124" s="9"/>
-      <c r="O124" s="9"/>
-      <c r="P124" s="9"/>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O124" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P124" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLM-DRL MEC task scheduling/comms</t>
+        </is>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="7" t="n">
@@ -16108,9 +18216,21 @@
       <c r="M125" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="N125" s="9"/>
-      <c r="O125" s="9"/>
-      <c r="P125" s="9"/>
+      <c r="N125" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O125" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P125" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low-altitude airspace path planning + capacity/collision risk</t>
+        </is>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="7" t="n">
@@ -16150,9 +18270,21 @@
       <c r="M126" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="N126" s="9"/>
-      <c r="O126" s="9"/>
-      <c r="P126" s="9"/>
+      <c r="N126" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O126" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P126" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UTM air-corridor/route-network planning</t>
+        </is>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="7" t="n">
@@ -16192,9 +18324,21 @@
       <c r="M127" s="7" t="s">
         <v>1244</v>
       </c>
-      <c r="N127" s="9"/>
-      <c r="O127" s="9"/>
-      <c r="P127" s="9"/>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P127" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-UAV cooperative path planning + conflict resolution</t>
+        </is>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="7" t="n">
@@ -16234,9 +18378,21 @@
       <c r="M128" s="7" t="s">
         <v>1249</v>
       </c>
-      <c r="N128" s="9"/>
-      <c r="O128" s="9"/>
-      <c r="P128" s="9"/>
+      <c r="N128" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O128" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1</t>
+        </is>
+      </c>
+      <c r="P128" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-UAV coded-caching data delivery (comms)</t>
+        </is>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="7" t="n">
@@ -16276,9 +18432,21 @@
       <c r="M129" s="7" t="s">
         <v>1254</v>
       </c>
-      <c r="N129" s="9"/>
-      <c r="O129" s="9"/>
-      <c r="P129" s="9"/>
+      <c r="N129" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O129" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P129" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-UAV task allocation (fleet coord; 5th include; stop)</t>
+        </is>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="7" t="n">
@@ -17021,150 +19189,150 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" display="10.1007/978-3-319-63387-9_5"/>
-    <hyperlink ref="L3" r:id="rId2" display="10.1109/TITS.2021.3082767"/>
-    <hyperlink ref="L4" r:id="rId3" display="10.1109/TITS.2022.3177627"/>
-    <hyperlink ref="L5" r:id="rId4" display="10.3390/electronics12173664"/>
-    <hyperlink ref="L6" r:id="rId5" display="10.1109/ACCESS.2021.3065926"/>
-    <hyperlink ref="L7" r:id="rId6" display="10.2514/6.2018-3676"/>
-    <hyperlink ref="L8" r:id="rId7" display="10.1109/ACCESS.2020.3000064"/>
-    <hyperlink ref="L9" r:id="rId8" display="10.1109/MCOM.2018.1700430"/>
-    <hyperlink ref="L10" r:id="rId9" display="10.1109/ACCESS.2019.2942944"/>
-    <hyperlink ref="L11" r:id="rId10" display="10.1109/JSEN.2022.3171293"/>
-    <hyperlink ref="L12" r:id="rId11" display="10.1109/ACCESS.2016.2537208"/>
-    <hyperlink ref="L13" r:id="rId12" display="10.1016/j.future.2019.05.007"/>
-    <hyperlink ref="L14" r:id="rId13" display="10.1109/LRA.2021.3056059"/>
-    <hyperlink ref="L16" r:id="rId14" display="10.1109/OJCOMS.2019.2955889"/>
-    <hyperlink ref="L17" r:id="rId15" display="10.1109/TVT.2019.2893615"/>
-    <hyperlink ref="L18" r:id="rId16" display="10.1109/TCCN.2021.3099114"/>
-    <hyperlink ref="L19" r:id="rId17" display="10.1109/ICASSP49357.2023.10095516"/>
-    <hyperlink ref="L20" r:id="rId18" display="10.1016/j.jairtraman.2020.101929"/>
-    <hyperlink ref="L21" r:id="rId19" display="10.1109/TGRS.2021.3104907"/>
-    <hyperlink ref="L22" r:id="rId20" display="10.3390/s20143856"/>
-    <hyperlink ref="L23" r:id="rId21" display="10.1109/TCOMM.2022.3224751"/>
-    <hyperlink ref="L24" r:id="rId22" display="10.3390/aerospace7030024"/>
-    <hyperlink ref="L25" r:id="rId23" display="10.1109/AERO.2019.8741970"/>
-    <hyperlink ref="L26" r:id="rId24" display="10.3390/eng4010025"/>
-    <hyperlink ref="L27" r:id="rId25" display="10.1109/JLT.2022.3208451"/>
-    <hyperlink ref="L28" r:id="rId26" display="10.3390/s21082824"/>
-    <hyperlink ref="L29" r:id="rId27" display="10.1109/JIOT.2021.3118949"/>
-    <hyperlink ref="L30" r:id="rId28" display="10.1109/ICPR48806.2021.9413241"/>
-    <hyperlink ref="L31" r:id="rId29" display="10.1016/j.comcom.2020.12.005"/>
-    <hyperlink ref="L32" r:id="rId30" display="10.1142/S2301385018400022"/>
-    <hyperlink ref="L33" r:id="rId31" display="10.2514/6.2018-1266"/>
-    <hyperlink ref="L34" r:id="rId32" display="10.1109/ICIoT48696.2020.9089489"/>
-    <hyperlink ref="L35" r:id="rId33" display="10.1109/ACCESS.2021.3092039"/>
-    <hyperlink ref="L36" r:id="rId34" display="10.3390/drones5030095"/>
-    <hyperlink ref="L37" r:id="rId35" display="10.1109/TIV.2023.3237329"/>
-    <hyperlink ref="L38" r:id="rId36" display="10.1109/JSEN.2021.3068444"/>
-    <hyperlink ref="L39" r:id="rId37" display="10.1007/s11042-023-15333-w"/>
-    <hyperlink ref="L40" r:id="rId38" display="10.3390/drones7060383"/>
-    <hyperlink ref="L41" r:id="rId39" display="10.3390/s21061947"/>
-    <hyperlink ref="L42" r:id="rId40" display="10.1109/TVT.2020.2964110"/>
-    <hyperlink ref="L43" r:id="rId41" display="10.1109/TVT.2023.3254604"/>
-    <hyperlink ref="L44" r:id="rId42" display="10.1109/TIM.2022.3198490"/>
-    <hyperlink ref="L45" r:id="rId43" display="10.3390/drones7010022"/>
-    <hyperlink ref="L46" r:id="rId44" display="10.3390/s23177650"/>
-    <hyperlink ref="L47" r:id="rId45" display="10.1186/s41074-019-0059-x"/>
-    <hyperlink ref="L48" r:id="rId46" display="10.1109/TVT.2020.3042128"/>
-    <hyperlink ref="L49" r:id="rId47" display="10.1038/s41598-023-33018-0"/>
-    <hyperlink ref="L50" r:id="rId48" display="10.3390/s21154953"/>
-    <hyperlink ref="L51" r:id="rId49" display="10.1109/TASE.2020.3010887"/>
-    <hyperlink ref="L52" r:id="rId50" display="10.1109/LGRS.2021.3085495"/>
-    <hyperlink ref="L53" r:id="rId51" display="10.1109/TETC.2021.3104555"/>
-    <hyperlink ref="L54" r:id="rId52" display="10.1016/j.paerosci.2020.100617"/>
-    <hyperlink ref="L55" r:id="rId53" display="10.1109/IWCMC.2019.8766732"/>
-    <hyperlink ref="L56" r:id="rId54" display="10.1007/s11227-020-03264-4"/>
-    <hyperlink ref="L57" r:id="rId55" display="10.1016/j.pmcj.2022.101569"/>
-    <hyperlink ref="L58" r:id="rId56" display="10.1109/TITS.2020.3019397"/>
-    <hyperlink ref="L59" r:id="rId57" display="10.1109/TIM.2022.3188050"/>
-    <hyperlink ref="L60" r:id="rId58" display="10.1016/S2589-7500(23)00161-9"/>
-    <hyperlink ref="L61" r:id="rId59" display="10.1109/AVSS.2017.8078539"/>
-    <hyperlink ref="L62" r:id="rId60" display="10.2514/1.G003724"/>
-    <hyperlink ref="L63" r:id="rId61" display="10.1109/CCNC.2019.8651804"/>
-    <hyperlink ref="L64" r:id="rId62" display="10.1016/j.seta.2023.103202"/>
-    <hyperlink ref="L65" r:id="rId63" display="10.3390/s21103374"/>
-    <hyperlink ref="L66" r:id="rId64" display="10.3390/drones6110317"/>
-    <hyperlink ref="L67" r:id="rId65" display="10.1109/RADAR.2016.7485236"/>
-    <hyperlink ref="L68" r:id="rId66" display="10.1109/TVT.2021.3093318"/>
-    <hyperlink ref="L69" r:id="rId67" display="10.1145/2935620.2935632"/>
-    <hyperlink ref="L70" r:id="rId68" display="10.1016/j.jisa.2019.06.010"/>
-    <hyperlink ref="L71" r:id="rId69" display="10.2352/ISSN.2470-1173.2017.10.IMAWM-168"/>
-    <hyperlink ref="L72" r:id="rId70" display="10.1109/JSEN.2023.3242985"/>
-    <hyperlink ref="L73" r:id="rId71" display="10.3390/drones7070446"/>
-    <hyperlink ref="L74" r:id="rId72" display="10.1109/TVT.2018.2884767"/>
-    <hyperlink ref="L75" r:id="rId73" display="10.1109/AVSS52988.2021.9663841"/>
-    <hyperlink ref="L76" r:id="rId74" display="10.3390/s23094202"/>
-    <hyperlink ref="L77" r:id="rId75" display="10.1109/ACCESS.2023.3293124"/>
-    <hyperlink ref="L78" r:id="rId76" display="10.1109/TIV.2021.3123110"/>
-    <hyperlink ref="L79" r:id="rId77" display="10.1109/JSYST.2021.3101283"/>
-    <hyperlink ref="L80" r:id="rId78" display="10.3390/aerospace9010031"/>
-    <hyperlink ref="L81" r:id="rId79" display="10.1109/LRA.2022.3145498"/>
-    <hyperlink ref="L82" r:id="rId80" display="10.1109/ICCVW54120.2021.00142"/>
-    <hyperlink ref="L83" r:id="rId81" display="10.1109/CVPR46437.2021.00699"/>
-    <hyperlink ref="L84" r:id="rId82" display="10.23919/ChiCC.2019.8865525"/>
-    <hyperlink ref="L85" r:id="rId83" display="10.3390/ijgi10050338"/>
-    <hyperlink ref="L86" r:id="rId84" display="10.1016/j.coldregions.2023.103938"/>
-    <hyperlink ref="L87" r:id="rId85" display="10.1109/ICIoT48696.2020.9089657"/>
-    <hyperlink ref="L88" r:id="rId86" display="10.1109/TITS.2020.3048364"/>
-    <hyperlink ref="L89" r:id="rId87" display="10.1109/JSEN.2021.3105229"/>
-    <hyperlink ref="L90" r:id="rId88" display="10.1109/ACCESS.2022.3172787"/>
-    <hyperlink ref="L91" r:id="rId89" display="10.3390/electronics11172669"/>
-    <hyperlink ref="L92" r:id="rId90" display="10.1016/j.trc.2021.103122"/>
-    <hyperlink ref="L93" r:id="rId91" display="10.1109/ACCESS.2020.2979339"/>
-    <hyperlink ref="L94" r:id="rId92" display="10.1109/ICRA48891.2023.10161355"/>
-    <hyperlink ref="L95" r:id="rId93" display="10.3390/rs15184617"/>
-    <hyperlink ref="L96" r:id="rId94" display="10.1109/MCOMSTD.001.2000032"/>
-    <hyperlink ref="L97" r:id="rId95" display="10.1109/TNSM.2022.3201817"/>
-    <hyperlink ref="L98" r:id="rId96" display="10.1109/ICICCS48265.2020.9121150"/>
-    <hyperlink ref="L99" r:id="rId97" display="10.1109/TITS.2021.3052229"/>
-    <hyperlink ref="L100" r:id="rId98" display="10.1109/TII.2022.3232777"/>
-    <hyperlink ref="L101" r:id="rId99" display="10.3390/drones6020028"/>
-    <hyperlink ref="L102" r:id="rId100" display="10.1016/j.jweia.2022.105136"/>
-    <hyperlink ref="L103" r:id="rId101" display="10.1016/j.trc.2022.103666"/>
-    <hyperlink ref="L104" r:id="rId102" display="10.1109/TIFS.2019.2959899"/>
-    <hyperlink ref="L105" r:id="rId103" display="10.1016/j.jestch.2021.06.008"/>
-    <hyperlink ref="L106" r:id="rId104" display="10.1109/BigMM.2017.57"/>
-    <hyperlink ref="L107" r:id="rId105" display="10.1109/AVSS.2019.8909830"/>
-    <hyperlink ref="L108" r:id="rId106" display="10.3390/s22083072"/>
-    <hyperlink ref="L109" r:id="rId107" display="10.3390/drones7010026"/>
-    <hyperlink ref="L110" r:id="rId108" display="10.15587/1729-4061.2022.260084"/>
-    <hyperlink ref="L111" r:id="rId109" display="10.1109/TITS.2022.3170643"/>
-    <hyperlink ref="L112" r:id="rId110" display="10.1109/TCCN.2025.3601015"/>
-    <hyperlink ref="L113" r:id="rId111" display="10.1109/TWC.2025.3583950"/>
-    <hyperlink ref="L114" r:id="rId112" display="10.1109/TGRS.2024.3395483"/>
-    <hyperlink ref="L115" r:id="rId113" display="10.1109/MWC.2025.3630114"/>
-    <hyperlink ref="L116" r:id="rId114" display="10.3390/drones8070337"/>
-    <hyperlink ref="L117" r:id="rId115" display="10.1109/ACCESS.2024.3420730"/>
-    <hyperlink ref="L118" r:id="rId116" display="10.1109/ACCESS.2024.3363413"/>
-    <hyperlink ref="L119" r:id="rId117" display="10.1109/TITS.2024.3509339"/>
-    <hyperlink ref="L120" r:id="rId118" display="10.1109/TITS.2024.3511453"/>
-    <hyperlink ref="L121" r:id="rId119" display="10.1145/3617992"/>
-    <hyperlink ref="L122" r:id="rId120" display="10.3390/drones9030159"/>
-    <hyperlink ref="L123" r:id="rId121" display="10.1109/TCOMM.2025.3642742"/>
-    <hyperlink ref="L124" r:id="rId122" display="10.1109/TCCN.2025.3645407"/>
-    <hyperlink ref="L125" r:id="rId123" display="10.3390/drones9050320"/>
-    <hyperlink ref="L126" r:id="rId124" display="10.1016/j.tre.2024.103859"/>
-    <hyperlink ref="L127" r:id="rId125" display="10.1109/TCE.2025.3593383"/>
-    <hyperlink ref="L128" r:id="rId126" display="10.1109/JIOT.2025.3562872"/>
-    <hyperlink ref="L129" r:id="rId127" display="10.1016/j.comcom.2024.107986"/>
-    <hyperlink ref="L130" r:id="rId128" display="10.1109/ICRA57147.2024.10610957"/>
-    <hyperlink ref="L131" r:id="rId129" display="10.1109/TGRS.2025.3574963"/>
-    <hyperlink ref="L132" r:id="rId130" display="10.1109/JAS.2023.123945"/>
-    <hyperlink ref="L133" r:id="rId131" display="10.1109/JIOT.2025.3605043"/>
-    <hyperlink ref="L134" r:id="rId132" display="10.1109/TGRS.2026.3658082"/>
-    <hyperlink ref="L135" r:id="rId133" display="10.3390/s24082427"/>
-    <hyperlink ref="L136" r:id="rId134" display="10.1145/3723871"/>
-    <hyperlink ref="L137" r:id="rId135" display="10.1109/CVPRW67362.2025.00663"/>
-    <hyperlink ref="L138" r:id="rId136" display="10.3390/drones8110638"/>
-    <hyperlink ref="L139" r:id="rId137" display="10.1109/TIFS.2026.3675426"/>
-    <hyperlink ref="L140" r:id="rId138" display="10.1109/JSEN.2024.3505939"/>
-    <hyperlink ref="L141" r:id="rId139" display="10.1016/j.ast.2025.109947"/>
-    <hyperlink ref="L142" r:id="rId140" display="10.3390/rs17040705"/>
-    <hyperlink ref="L143" r:id="rId141" display="10.1109/ACCESS.2024.3481148"/>
-    <hyperlink ref="L144" r:id="rId142" display="10.3390/drones8110680"/>
-    <hyperlink ref="L145" r:id="rId143" display="10.1109/TGRS.2025.3567751"/>
-    <hyperlink ref="L146" r:id="rId144" display="10.1016/j.tra.2024.104338"/>
+    <hyperlink ref="L2" ns1:id="rId1" display="10.1007/978-3-319-63387-9_5"/>
+    <hyperlink ref="L3" ns1:id="rId2" display="10.1109/TITS.2021.3082767"/>
+    <hyperlink ref="L4" ns1:id="rId3" display="10.1109/TITS.2022.3177627"/>
+    <hyperlink ref="L5" ns1:id="rId4" display="10.3390/electronics12173664"/>
+    <hyperlink ref="L6" ns1:id="rId5" display="10.1109/ACCESS.2021.3065926"/>
+    <hyperlink ref="L7" ns1:id="rId6" display="10.2514/6.2018-3676"/>
+    <hyperlink ref="L8" ns1:id="rId7" display="10.1109/ACCESS.2020.3000064"/>
+    <hyperlink ref="L9" ns1:id="rId8" display="10.1109/MCOM.2018.1700430"/>
+    <hyperlink ref="L10" ns1:id="rId9" display="10.1109/ACCESS.2019.2942944"/>
+    <hyperlink ref="L11" ns1:id="rId10" display="10.1109/JSEN.2022.3171293"/>
+    <hyperlink ref="L12" ns1:id="rId11" display="10.1109/ACCESS.2016.2537208"/>
+    <hyperlink ref="L13" ns1:id="rId12" display="10.1016/j.future.2019.05.007"/>
+    <hyperlink ref="L14" ns1:id="rId13" display="10.1109/LRA.2021.3056059"/>
+    <hyperlink ref="L16" ns1:id="rId14" display="10.1109/OJCOMS.2019.2955889"/>
+    <hyperlink ref="L17" ns1:id="rId15" display="10.1109/TVT.2019.2893615"/>
+    <hyperlink ref="L18" ns1:id="rId16" display="10.1109/TCCN.2021.3099114"/>
+    <hyperlink ref="L19" ns1:id="rId17" display="10.1109/ICASSP49357.2023.10095516"/>
+    <hyperlink ref="L20" ns1:id="rId18" display="10.1016/j.jairtraman.2020.101929"/>
+    <hyperlink ref="L21" ns1:id="rId19" display="10.1109/TGRS.2021.3104907"/>
+    <hyperlink ref="L22" ns1:id="rId20" display="10.3390/s20143856"/>
+    <hyperlink ref="L23" ns1:id="rId21" display="10.1109/TCOMM.2022.3224751"/>
+    <hyperlink ref="L24" ns1:id="rId22" display="10.3390/aerospace7030024"/>
+    <hyperlink ref="L25" ns1:id="rId23" display="10.1109/AERO.2019.8741970"/>
+    <hyperlink ref="L26" ns1:id="rId24" display="10.3390/eng4010025"/>
+    <hyperlink ref="L27" ns1:id="rId25" display="10.1109/JLT.2022.3208451"/>
+    <hyperlink ref="L28" ns1:id="rId26" display="10.3390/s21082824"/>
+    <hyperlink ref="L29" ns1:id="rId27" display="10.1109/JIOT.2021.3118949"/>
+    <hyperlink ref="L30" ns1:id="rId28" display="10.1109/ICPR48806.2021.9413241"/>
+    <hyperlink ref="L31" ns1:id="rId29" display="10.1016/j.comcom.2020.12.005"/>
+    <hyperlink ref="L32" ns1:id="rId30" display="10.1142/S2301385018400022"/>
+    <hyperlink ref="L33" ns1:id="rId31" display="10.2514/6.2018-1266"/>
+    <hyperlink ref="L34" ns1:id="rId32" display="10.1109/ICIoT48696.2020.9089489"/>
+    <hyperlink ref="L35" ns1:id="rId33" display="10.1109/ACCESS.2021.3092039"/>
+    <hyperlink ref="L36" ns1:id="rId34" display="10.3390/drones5030095"/>
+    <hyperlink ref="L37" ns1:id="rId35" display="10.1109/TIV.2023.3237329"/>
+    <hyperlink ref="L38" ns1:id="rId36" display="10.1109/JSEN.2021.3068444"/>
+    <hyperlink ref="L39" ns1:id="rId37" display="10.1007/s11042-023-15333-w"/>
+    <hyperlink ref="L40" ns1:id="rId38" display="10.3390/drones7060383"/>
+    <hyperlink ref="L41" ns1:id="rId39" display="10.3390/s21061947"/>
+    <hyperlink ref="L42" ns1:id="rId40" display="10.1109/TVT.2020.2964110"/>
+    <hyperlink ref="L43" ns1:id="rId41" display="10.1109/TVT.2023.3254604"/>
+    <hyperlink ref="L44" ns1:id="rId42" display="10.1109/TIM.2022.3198490"/>
+    <hyperlink ref="L45" ns1:id="rId43" display="10.3390/drones7010022"/>
+    <hyperlink ref="L46" ns1:id="rId44" display="10.3390/s23177650"/>
+    <hyperlink ref="L47" ns1:id="rId45" display="10.1186/s41074-019-0059-x"/>
+    <hyperlink ref="L48" ns1:id="rId46" display="10.1109/TVT.2020.3042128"/>
+    <hyperlink ref="L49" ns1:id="rId47" display="10.1038/s41598-023-33018-0"/>
+    <hyperlink ref="L50" ns1:id="rId48" display="10.3390/s21154953"/>
+    <hyperlink ref="L51" ns1:id="rId49" display="10.1109/TASE.2020.3010887"/>
+    <hyperlink ref="L52" ns1:id="rId50" display="10.1109/LGRS.2021.3085495"/>
+    <hyperlink ref="L53" ns1:id="rId51" display="10.1109/TETC.2021.3104555"/>
+    <hyperlink ref="L54" ns1:id="rId52" display="10.1016/j.paerosci.2020.100617"/>
+    <hyperlink ref="L55" ns1:id="rId53" display="10.1109/IWCMC.2019.8766732"/>
+    <hyperlink ref="L56" ns1:id="rId54" display="10.1007/s11227-020-03264-4"/>
+    <hyperlink ref="L57" ns1:id="rId55" display="10.1016/j.pmcj.2022.101569"/>
+    <hyperlink ref="L58" ns1:id="rId56" display="10.1109/TITS.2020.3019397"/>
+    <hyperlink ref="L59" ns1:id="rId57" display="10.1109/TIM.2022.3188050"/>
+    <hyperlink ref="L60" ns1:id="rId58" display="10.1016/S2589-7500(23)00161-9"/>
+    <hyperlink ref="L61" ns1:id="rId59" display="10.1109/AVSS.2017.8078539"/>
+    <hyperlink ref="L62" ns1:id="rId60" display="10.2514/1.G003724"/>
+    <hyperlink ref="L63" ns1:id="rId61" display="10.1109/CCNC.2019.8651804"/>
+    <hyperlink ref="L64" ns1:id="rId62" display="10.1016/j.seta.2023.103202"/>
+    <hyperlink ref="L65" ns1:id="rId63" display="10.3390/s21103374"/>
+    <hyperlink ref="L66" ns1:id="rId64" display="10.3390/drones6110317"/>
+    <hyperlink ref="L67" ns1:id="rId65" display="10.1109/RADAR.2016.7485236"/>
+    <hyperlink ref="L68" ns1:id="rId66" display="10.1109/TVT.2021.3093318"/>
+    <hyperlink ref="L69" ns1:id="rId67" display="10.1145/2935620.2935632"/>
+    <hyperlink ref="L70" ns1:id="rId68" display="10.1016/j.jisa.2019.06.010"/>
+    <hyperlink ref="L71" ns1:id="rId69" display="10.2352/ISSN.2470-1173.2017.10.IMAWM-168"/>
+    <hyperlink ref="L72" ns1:id="rId70" display="10.1109/JSEN.2023.3242985"/>
+    <hyperlink ref="L73" ns1:id="rId71" display="10.3390/drones7070446"/>
+    <hyperlink ref="L74" ns1:id="rId72" display="10.1109/TVT.2018.2884767"/>
+    <hyperlink ref="L75" ns1:id="rId73" display="10.1109/AVSS52988.2021.9663841"/>
+    <hyperlink ref="L76" ns1:id="rId74" display="10.3390/s23094202"/>
+    <hyperlink ref="L77" ns1:id="rId75" display="10.1109/ACCESS.2023.3293124"/>
+    <hyperlink ref="L78" ns1:id="rId76" display="10.1109/TIV.2021.3123110"/>
+    <hyperlink ref="L79" ns1:id="rId77" display="10.1109/JSYST.2021.3101283"/>
+    <hyperlink ref="L80" ns1:id="rId78" display="10.3390/aerospace9010031"/>
+    <hyperlink ref="L81" ns1:id="rId79" display="10.1109/LRA.2022.3145498"/>
+    <hyperlink ref="L82" ns1:id="rId80" display="10.1109/ICCVW54120.2021.00142"/>
+    <hyperlink ref="L83" ns1:id="rId81" display="10.1109/CVPR46437.2021.00699"/>
+    <hyperlink ref="L84" ns1:id="rId82" display="10.23919/ChiCC.2019.8865525"/>
+    <hyperlink ref="L85" ns1:id="rId83" display="10.3390/ijgi10050338"/>
+    <hyperlink ref="L86" ns1:id="rId84" display="10.1016/j.coldregions.2023.103938"/>
+    <hyperlink ref="L87" ns1:id="rId85" display="10.1109/ICIoT48696.2020.9089657"/>
+    <hyperlink ref="L88" ns1:id="rId86" display="10.1109/TITS.2020.3048364"/>
+    <hyperlink ref="L89" ns1:id="rId87" display="10.1109/JSEN.2021.3105229"/>
+    <hyperlink ref="L90" ns1:id="rId88" display="10.1109/ACCESS.2022.3172787"/>
+    <hyperlink ref="L91" ns1:id="rId89" display="10.3390/electronics11172669"/>
+    <hyperlink ref="L92" ns1:id="rId90" display="10.1016/j.trc.2021.103122"/>
+    <hyperlink ref="L93" ns1:id="rId91" display="10.1109/ACCESS.2020.2979339"/>
+    <hyperlink ref="L94" ns1:id="rId92" display="10.1109/ICRA48891.2023.10161355"/>
+    <hyperlink ref="L95" ns1:id="rId93" display="10.3390/rs15184617"/>
+    <hyperlink ref="L96" ns1:id="rId94" display="10.1109/MCOMSTD.001.2000032"/>
+    <hyperlink ref="L97" ns1:id="rId95" display="10.1109/TNSM.2022.3201817"/>
+    <hyperlink ref="L98" ns1:id="rId96" display="10.1109/ICICCS48265.2020.9121150"/>
+    <hyperlink ref="L99" ns1:id="rId97" display="10.1109/TITS.2021.3052229"/>
+    <hyperlink ref="L100" ns1:id="rId98" display="10.1109/TII.2022.3232777"/>
+    <hyperlink ref="L101" ns1:id="rId99" display="10.3390/drones6020028"/>
+    <hyperlink ref="L102" ns1:id="rId100" display="10.1016/j.jweia.2022.105136"/>
+    <hyperlink ref="L103" ns1:id="rId101" display="10.1016/j.trc.2022.103666"/>
+    <hyperlink ref="L104" ns1:id="rId102" display="10.1109/TIFS.2019.2959899"/>
+    <hyperlink ref="L105" ns1:id="rId103" display="10.1016/j.jestch.2021.06.008"/>
+    <hyperlink ref="L106" ns1:id="rId104" display="10.1109/BigMM.2017.57"/>
+    <hyperlink ref="L107" ns1:id="rId105" display="10.1109/AVSS.2019.8909830"/>
+    <hyperlink ref="L108" ns1:id="rId106" display="10.3390/s22083072"/>
+    <hyperlink ref="L109" ns1:id="rId107" display="10.3390/drones7010026"/>
+    <hyperlink ref="L110" ns1:id="rId108" display="10.15587/1729-4061.2022.260084"/>
+    <hyperlink ref="L111" ns1:id="rId109" display="10.1109/TITS.2022.3170643"/>
+    <hyperlink ref="L112" ns1:id="rId110" display="10.1109/TCCN.2025.3601015"/>
+    <hyperlink ref="L113" ns1:id="rId111" display="10.1109/TWC.2025.3583950"/>
+    <hyperlink ref="L114" ns1:id="rId112" display="10.1109/TGRS.2024.3395483"/>
+    <hyperlink ref="L115" ns1:id="rId113" display="10.1109/MWC.2025.3630114"/>
+    <hyperlink ref="L116" ns1:id="rId114" display="10.3390/drones8070337"/>
+    <hyperlink ref="L117" ns1:id="rId115" display="10.1109/ACCESS.2024.3420730"/>
+    <hyperlink ref="L118" ns1:id="rId116" display="10.1109/ACCESS.2024.3363413"/>
+    <hyperlink ref="L119" ns1:id="rId117" display="10.1109/TITS.2024.3509339"/>
+    <hyperlink ref="L120" ns1:id="rId118" display="10.1109/TITS.2024.3511453"/>
+    <hyperlink ref="L121" ns1:id="rId119" display="10.1145/3617992"/>
+    <hyperlink ref="L122" ns1:id="rId120" display="10.3390/drones9030159"/>
+    <hyperlink ref="L123" ns1:id="rId121" display="10.1109/TCOMM.2025.3642742"/>
+    <hyperlink ref="L124" ns1:id="rId122" display="10.1109/TCCN.2025.3645407"/>
+    <hyperlink ref="L125" ns1:id="rId123" display="10.3390/drones9050320"/>
+    <hyperlink ref="L126" ns1:id="rId124" display="10.1016/j.tre.2024.103859"/>
+    <hyperlink ref="L127" ns1:id="rId125" display="10.1109/TCE.2025.3593383"/>
+    <hyperlink ref="L128" ns1:id="rId126" display="10.1109/JIOT.2025.3562872"/>
+    <hyperlink ref="L129" ns1:id="rId127" display="10.1016/j.comcom.2024.107986"/>
+    <hyperlink ref="L130" ns1:id="rId128" display="10.1109/ICRA57147.2024.10610957"/>
+    <hyperlink ref="L131" ns1:id="rId129" display="10.1109/TGRS.2025.3574963"/>
+    <hyperlink ref="L132" ns1:id="rId130" display="10.1109/JAS.2023.123945"/>
+    <hyperlink ref="L133" ns1:id="rId131" display="10.1109/JIOT.2025.3605043"/>
+    <hyperlink ref="L134" ns1:id="rId132" display="10.1109/TGRS.2026.3658082"/>
+    <hyperlink ref="L135" ns1:id="rId133" display="10.3390/s24082427"/>
+    <hyperlink ref="L136" ns1:id="rId134" display="10.1145/3723871"/>
+    <hyperlink ref="L137" ns1:id="rId135" display="10.1109/CVPRW67362.2025.00663"/>
+    <hyperlink ref="L138" ns1:id="rId136" display="10.3390/drones8110638"/>
+    <hyperlink ref="L139" ns1:id="rId137" display="10.1109/TIFS.2026.3675426"/>
+    <hyperlink ref="L140" ns1:id="rId138" display="10.1109/JSEN.2024.3505939"/>
+    <hyperlink ref="L141" ns1:id="rId139" display="10.1016/j.ast.2025.109947"/>
+    <hyperlink ref="L142" ns1:id="rId140" display="10.3390/rs17040705"/>
+    <hyperlink ref="L143" ns1:id="rId141" display="10.1109/ACCESS.2024.3481148"/>
+    <hyperlink ref="L144" ns1:id="rId142" display="10.3390/drones8110680"/>
+    <hyperlink ref="L145" ns1:id="rId143" display="10.1109/TGRS.2025.3567751"/>
+    <hyperlink ref="L146" ns1:id="rId144" display="10.1016/j.tra.2024.104338"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -17173,12 +19341,12 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId145"/>
+  <drawing ns1:id="rId145"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -17289,9 +19457,21 @@
       <c r="M2" s="7" t="s">
         <v>1347</v>
       </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P2" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AIS ship trajectory prediction (traffic/collision)</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
@@ -17329,9 +19509,21 @@
       <c r="M3" s="7" t="s">
         <v>1352</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YOLOv7-sea maritime UAV SAR detection</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -17371,9 +19563,21 @@
       <c r="M4" s="7" t="s">
         <v>1358</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLREGs USV path planning + collision avoidance (DRL)</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
@@ -17413,9 +19617,21 @@
       <c r="M5" s="7" t="s">
         <v>1364</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MASS risk assessment (formal safety)</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
@@ -17455,9 +19671,21 @@
       <c r="M6" s="7" t="s">
         <v>1370</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooperative USV-UAV marine SAR</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
@@ -17497,9 +19725,21 @@
       <c r="M7" s="7" t="s">
         <v>1376</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLREGs real-time path planning (APF)</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
@@ -17539,9 +19779,21 @@
       <c r="M8" s="7" t="s">
         <v>1381</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maritime SAR via UAV-USV group computing</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -17581,9 +19833,21 @@
       <c r="M9" s="7" t="s">
         <v>1387</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USV collision avoidance (DRL)</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
@@ -17621,9 +19885,21 @@
       <c r="M10" s="7" t="s">
         <v>1392</v>
       </c>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USV collision avoidance A*/DWA</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
@@ -17663,9 +19939,21 @@
       <c r="M11" s="7" t="s">
         <v>1397</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-UAV coverage path planning for maritime SAR</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
@@ -17705,9 +19993,21 @@
       <c r="M12" s="7" t="s">
         <v>1402</v>
       </c>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ship trajectory prediction (GAT-LSTM)</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
@@ -17747,9 +20047,21 @@
       <c r="M13" s="7" t="s">
         <v>1407</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DRL collision avoidance autonomous ship</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
@@ -17789,9 +20101,21 @@
       <c r="M14" s="7" t="s">
         <v>1413</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E4</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marine-heatwave ecology (bull kelp)</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
@@ -17831,9 +20155,21 @@
       <c r="M15" s="7" t="s">
         <v>1418</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MPAPF ship motion planning (COLREGs)</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="n">
@@ -17873,9 +20209,21 @@
       <c r="M16" s="7" t="s">
         <v>1423</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ship collision avoidance COLREGs (MPC)</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
@@ -17915,9 +20263,21 @@
       <c r="M17" s="7" t="s">
         <v>1428</v>
       </c>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PPO/RVO multi-USV collision-avoidance path planning</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
@@ -17957,9 +20317,21 @@
       <c r="M18" s="7" t="s">
         <v>1433</v>
       </c>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AIS ML route planning for MASS</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
@@ -17999,9 +20371,21 @@
       <c r="M19" s="7" t="s">
         <v>1438</v>
       </c>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLREGs multiship collision avoidance (DRL)</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
@@ -18041,9 +20425,21 @@
       <c r="M20" s="7" t="s">
         <v>1444</v>
       </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DL small-ship detection (autonomous ship)</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
@@ -18083,9 +20479,21 @@
       <c r="M21" s="7" t="s">
         <v>1449</v>
       </c>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DL ship detection from drone, maritime surveillance</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
@@ -18125,9 +20533,21 @@
       <c r="M22" s="7" t="s">
         <v>1454</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generalized velocity obstacle ship collision avoidance (20th include; stop)</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="n">
@@ -20223,9 +22643,21 @@
       <c r="M72" s="7" t="s">
         <v>1713</v>
       </c>
-      <c r="N72" s="9"/>
-      <c r="O72" s="9"/>
-      <c r="P72" s="9"/>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MarineSeg USV scene segmentation (perception)</t>
+        </is>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="n">
@@ -20265,9 +22697,21 @@
       <c r="M73" s="7" t="s">
         <v>1718</v>
       </c>
-      <c r="N73" s="9"/>
-      <c r="O73" s="9"/>
-      <c r="P73" s="9"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WaterScenes 4D radar-camera dataset (USV/UAV)</t>
+        </is>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="n">
@@ -20309,9 +22753,21 @@
       <c r="M74" s="7" t="s">
         <v>1724</v>
       </c>
-      <c r="N74" s="9"/>
-      <c r="O74" s="9"/>
-      <c r="P74" s="9"/>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exclude</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="P74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maritime-UAV object-detection review</t>
+        </is>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="n">
@@ -20351,9 +22807,21 @@
       <c r="M75" s="7" t="s">
         <v>1729</v>
       </c>
-      <c r="N75" s="9"/>
-      <c r="O75" s="9"/>
-      <c r="P75" s="9"/>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P75" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooperative USV-UAV path following for SAR</t>
+        </is>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="n">
@@ -20393,9 +22861,21 @@
       <c r="M76" s="7" t="s">
         <v>1735</v>
       </c>
-      <c r="N76" s="9"/>
-      <c r="O76" s="9"/>
-      <c r="P76" s="9"/>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adaptive USV collision avoidance (MARL)</t>
+        </is>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="n">
@@ -20435,9 +22915,21 @@
       <c r="M77" s="7" t="s">
         <v>1740</v>
       </c>
-      <c r="N77" s="9"/>
-      <c r="O77" s="9"/>
-      <c r="P77" s="9"/>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-USV dynamic path planning (PPO; 5th; stop)</t>
+        </is>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="n">
@@ -21258,101 +23750,101 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" display="10.1016/j.tre.2023.103152"/>
-    <hyperlink ref="L3" r:id="rId2" display="10.1109/WACVW58289.2023.00029"/>
-    <hyperlink ref="L4" r:id="rId3" display="10.1016/j.apor.2021.102759"/>
-    <hyperlink ref="L5" r:id="rId4" display="10.1016/j.ress.2020.107324"/>
-    <hyperlink ref="L6" r:id="rId5" display="10.1016/j.isatra.2023.01.007"/>
-    <hyperlink ref="L7" r:id="rId6" display="10.1017/S0373463318000796"/>
-    <hyperlink ref="L8" r:id="rId7" display="10.1109/TII.2020.2974047"/>
-    <hyperlink ref="L9" r:id="rId8" display="10.1016/j.oceaneng.2020.107001"/>
-    <hyperlink ref="L10" r:id="rId9" display="10.1109/MITS.2022.3229109"/>
-    <hyperlink ref="L11" r:id="rId10" display="10.1016/j.cie.2021.107612"/>
-    <hyperlink ref="L12" r:id="rId11" display="10.1016/j.oceaneng.2023.116159"/>
-    <hyperlink ref="L13" r:id="rId12" display="10.1016/j.oceaneng.2021.109216"/>
-    <hyperlink ref="L14" r:id="rId13" display="10.3389/fmars.2019.00084"/>
-    <hyperlink ref="L15" r:id="rId14" display="10.1016/j.isatra.2022.09.007"/>
-    <hyperlink ref="L16" r:id="rId15" display="10.1109/TITS.2016.2551780"/>
-    <hyperlink ref="L17" r:id="rId16" display="10.1016/j.oceaneng.2023.114005"/>
-    <hyperlink ref="L18" r:id="rId17" display="10.1016/j.tre.2023.103171"/>
-    <hyperlink ref="L19" r:id="rId18" display="10.1016/j.oceaneng.2019.106436"/>
-    <hyperlink ref="L20" r:id="rId19" display="10.1016/j.ssci.2020.104812"/>
-    <hyperlink ref="L21" r:id="rId20" display="10.1016/j.oceaneng.2023.115440"/>
-    <hyperlink ref="L22" r:id="rId21" display="10.1016/j.oceaneng.2018.12.053"/>
-    <hyperlink ref="L23" r:id="rId22" display="10.1016/j.oceaneng.2023.114205"/>
-    <hyperlink ref="L24" r:id="rId23" display="10.1016/j.oceaneng.2023.115208"/>
-    <hyperlink ref="L25" r:id="rId24" display="10.1109/ACCESS.2021.3053956"/>
-    <hyperlink ref="L26" r:id="rId25" display="10.1016/j.oceaneng.2020.107910"/>
-    <hyperlink ref="L27" r:id="rId26" display="10.1109/LRA.2021.3067271"/>
-    <hyperlink ref="L28" r:id="rId27" display="10.1016/j.neucom.2021.09.071"/>
-    <hyperlink ref="L29" r:id="rId28" display="10.1109/TGRS.2018.2848901"/>
-    <hyperlink ref="L30" r:id="rId29" display="10.1016/j.ress.2023.109103"/>
-    <hyperlink ref="L31" r:id="rId30" display="10.3389/fmars.2022.1084763"/>
-    <hyperlink ref="L32" r:id="rId31" display="10.1016/j.oceaneng.2023.113737"/>
-    <hyperlink ref="L33" r:id="rId32" display="10.1109/ACCESS.2021.3049238"/>
-    <hyperlink ref="L34" r:id="rId33" display="10.1016/j.ssci.2020.104939"/>
-    <hyperlink ref="L35" r:id="rId34" display="10.1002/rob.21935"/>
-    <hyperlink ref="L36" r:id="rId35" display="10.1016/j.ress.2023.109554"/>
-    <hyperlink ref="L37" r:id="rId36" display="10.1016/j.oceaneng.2020.107704"/>
-    <hyperlink ref="L38" r:id="rId37" display="10.1016/j.oceaneng.2018.04.018"/>
-    <hyperlink ref="L39" r:id="rId38" display="10.3390/rs14133049"/>
-    <hyperlink ref="L40" r:id="rId39" display="10.1145/3571733"/>
-    <hyperlink ref="L41" r:id="rId40" display="10.1109/ACCESS.2019.2953326"/>
-    <hyperlink ref="L42" r:id="rId41" display="10.3390/jmse11112065"/>
-    <hyperlink ref="L43" r:id="rId42" display="10.1016/j.oceaneng.2022.110749"/>
-    <hyperlink ref="L44" r:id="rId43" display="10.1016/j.oceaneng.2022.110531"/>
-    <hyperlink ref="L45" r:id="rId44" display="10.3233/ica-210649"/>
-    <hyperlink ref="L46" r:id="rId45" display="10.1007/s13437-022-00277-z"/>
-    <hyperlink ref="L47" r:id="rId46" display="10.1016/j.ocecoaman.2023.106515"/>
-    <hyperlink ref="L48" r:id="rId47" display="10.1016/j.neucom.2015.12.028"/>
-    <hyperlink ref="L49" r:id="rId48" display="10.1016/j.oceaneng.2022.111847"/>
-    <hyperlink ref="L50" r:id="rId49" display="10.1109/TITS.2020.2976567"/>
-    <hyperlink ref="L51" r:id="rId50" display="10.1016/j.oceaneng.2021.109147"/>
-    <hyperlink ref="L52" r:id="rId51" display="10.1177/1748006X211051829"/>
-    <hyperlink ref="L53" r:id="rId52" display="10.3390/su14010198"/>
-    <hyperlink ref="L54" r:id="rId53" display="10.1016/j.ocecoaman.2023.106689"/>
-    <hyperlink ref="L55" r:id="rId54" display="10.1109/IROS40897.2019.8968131"/>
-    <hyperlink ref="L56" r:id="rId55" display="10.1016/j.oceaneng.2023.114156"/>
-    <hyperlink ref="L57" r:id="rId56" display="10.1109/TITS.2022.3151826"/>
-    <hyperlink ref="L58" r:id="rId57" display="10.1016/j.oceaneng.2021.108569"/>
-    <hyperlink ref="L59" r:id="rId58" display="10.1016/j.ress.2019.106584"/>
-    <hyperlink ref="L60" r:id="rId59" display="10.1109/ACCESS.2020.3022600"/>
-    <hyperlink ref="L61" r:id="rId60" display="10.1016/j.apor.2021.102755"/>
-    <hyperlink ref="L62" r:id="rId61" display="10.1016/j.oceaneng.2020.107913"/>
-    <hyperlink ref="L63" r:id="rId62" display="10.1016/j.ress.2022.108709"/>
-    <hyperlink ref="L64" r:id="rId63" display="10.3390/jmse10101460"/>
-    <hyperlink ref="L65" r:id="rId64" display="10.1016/j.ress.2021.107806"/>
-    <hyperlink ref="L66" r:id="rId65" display="10.1109/ACCESS.2022.3154363"/>
-    <hyperlink ref="L67" r:id="rId66" display="10.1016/j.eswa.2023.120825"/>
-    <hyperlink ref="L68" r:id="rId67" display="10.1016/j.ssci.2020.104758"/>
-    <hyperlink ref="L69" r:id="rId68" display="10.3390/jmse10010003"/>
-    <hyperlink ref="L70" r:id="rId69" display="10.3390/rs14164070"/>
-    <hyperlink ref="L71" r:id="rId70" display="10.1016/j.ssci.2020.104919"/>
-    <hyperlink ref="L72" r:id="rId71" display="10.1016/j.neucom.2025.132597"/>
-    <hyperlink ref="L73" r:id="rId72" display="10.1109/TITS.2024.3415772"/>
-    <hyperlink ref="L74" r:id="rId73" display="10.1016/j.engappai.2023.107513"/>
-    <hyperlink ref="L75" r:id="rId74" display="10.1109/TIV.2023.3317336"/>
-    <hyperlink ref="L76" r:id="rId75" display="10.1016/j.aei.2025.103355"/>
-    <hyperlink ref="L77" r:id="rId76" display="10.1016/j.oceaneng.2025.120907"/>
-    <hyperlink ref="L78" r:id="rId77" display="10.1109/TVT.2023.3338518"/>
-    <hyperlink ref="L79" r:id="rId78" display="10.1016/j.oceaneng.2024.117210"/>
-    <hyperlink ref="L80" r:id="rId79" display="10.1016/j.oceaneng.2026.124487"/>
-    <hyperlink ref="L81" r:id="rId80" display="10.21278/brod77204"/>
-    <hyperlink ref="L82" r:id="rId81" display="10.1016/j.eswa.2024.124388"/>
-    <hyperlink ref="L83" r:id="rId82" display="10.1016/j.tre.2023.103367"/>
-    <hyperlink ref="L84" r:id="rId83" display="10.1109/TCYB.2025.3556042"/>
-    <hyperlink ref="L85" r:id="rId84" display="10.1016/j.oceaneng.2024.120128"/>
-    <hyperlink ref="L86" r:id="rId85" display="10.1016/j.oceaneng.2025.124120"/>
-    <hyperlink ref="L87" r:id="rId86" display="10.1007/S10346-024-02337-2"/>
-    <hyperlink ref="L88" r:id="rId87" display="10.1109/TASE.2024.3375300"/>
-    <hyperlink ref="L89" r:id="rId88" display="10.1016/j.oceaneng.2025.120335"/>
-    <hyperlink ref="L90" r:id="rId89" display="10.1016/j.ress.2024.110080"/>
-    <hyperlink ref="L91" r:id="rId90" display="10.1109/TVT.2024.3384570"/>
-    <hyperlink ref="L92" r:id="rId91" display="10.1016/j.engappai.2023.107625"/>
-    <hyperlink ref="L93" r:id="rId92" display="10.1109/JIOT.2023.3325234"/>
-    <hyperlink ref="L94" r:id="rId93" display="10.1016/j.asoc.2025.113416"/>
-    <hyperlink ref="L95" r:id="rId94" display="10.1016/j.ress.2024.110547"/>
-    <hyperlink ref="L96" r:id="rId95" display="10.1016/j.knosys.2024.112205"/>
+    <hyperlink ref="L2" ns1:id="rId1" display="10.1016/j.tre.2023.103152"/>
+    <hyperlink ref="L3" ns1:id="rId2" display="10.1109/WACVW58289.2023.00029"/>
+    <hyperlink ref="L4" ns1:id="rId3" display="10.1016/j.apor.2021.102759"/>
+    <hyperlink ref="L5" ns1:id="rId4" display="10.1016/j.ress.2020.107324"/>
+    <hyperlink ref="L6" ns1:id="rId5" display="10.1016/j.isatra.2023.01.007"/>
+    <hyperlink ref="L7" ns1:id="rId6" display="10.1017/S0373463318000796"/>
+    <hyperlink ref="L8" ns1:id="rId7" display="10.1109/TII.2020.2974047"/>
+    <hyperlink ref="L9" ns1:id="rId8" display="10.1016/j.oceaneng.2020.107001"/>
+    <hyperlink ref="L10" ns1:id="rId9" display="10.1109/MITS.2022.3229109"/>
+    <hyperlink ref="L11" ns1:id="rId10" display="10.1016/j.cie.2021.107612"/>
+    <hyperlink ref="L12" ns1:id="rId11" display="10.1016/j.oceaneng.2023.116159"/>
+    <hyperlink ref="L13" ns1:id="rId12" display="10.1016/j.oceaneng.2021.109216"/>
+    <hyperlink ref="L14" ns1:id="rId13" display="10.3389/fmars.2019.00084"/>
+    <hyperlink ref="L15" ns1:id="rId14" display="10.1016/j.isatra.2022.09.007"/>
+    <hyperlink ref="L16" ns1:id="rId15" display="10.1109/TITS.2016.2551780"/>
+    <hyperlink ref="L17" ns1:id="rId16" display="10.1016/j.oceaneng.2023.114005"/>
+    <hyperlink ref="L18" ns1:id="rId17" display="10.1016/j.tre.2023.103171"/>
+    <hyperlink ref="L19" ns1:id="rId18" display="10.1016/j.oceaneng.2019.106436"/>
+    <hyperlink ref="L20" ns1:id="rId19" display="10.1016/j.ssci.2020.104812"/>
+    <hyperlink ref="L21" ns1:id="rId20" display="10.1016/j.oceaneng.2023.115440"/>
+    <hyperlink ref="L22" ns1:id="rId21" display="10.1016/j.oceaneng.2018.12.053"/>
+    <hyperlink ref="L23" ns1:id="rId22" display="10.1016/j.oceaneng.2023.114205"/>
+    <hyperlink ref="L24" ns1:id="rId23" display="10.1016/j.oceaneng.2023.115208"/>
+    <hyperlink ref="L25" ns1:id="rId24" display="10.1109/ACCESS.2021.3053956"/>
+    <hyperlink ref="L26" ns1:id="rId25" display="10.1016/j.oceaneng.2020.107910"/>
+    <hyperlink ref="L27" ns1:id="rId26" display="10.1109/LRA.2021.3067271"/>
+    <hyperlink ref="L28" ns1:id="rId27" display="10.1016/j.neucom.2021.09.071"/>
+    <hyperlink ref="L29" ns1:id="rId28" display="10.1109/TGRS.2018.2848901"/>
+    <hyperlink ref="L30" ns1:id="rId29" display="10.1016/j.ress.2023.109103"/>
+    <hyperlink ref="L31" ns1:id="rId30" display="10.3389/fmars.2022.1084763"/>
+    <hyperlink ref="L32" ns1:id="rId31" display="10.1016/j.oceaneng.2023.113737"/>
+    <hyperlink ref="L33" ns1:id="rId32" display="10.1109/ACCESS.2021.3049238"/>
+    <hyperlink ref="L34" ns1:id="rId33" display="10.1016/j.ssci.2020.104939"/>
+    <hyperlink ref="L35" ns1:id="rId34" display="10.1002/rob.21935"/>
+    <hyperlink ref="L36" ns1:id="rId35" display="10.1016/j.ress.2023.109554"/>
+    <hyperlink ref="L37" ns1:id="rId36" display="10.1016/j.oceaneng.2020.107704"/>
+    <hyperlink ref="L38" ns1:id="rId37" display="10.1016/j.oceaneng.2018.04.018"/>
+    <hyperlink ref="L39" ns1:id="rId38" display="10.3390/rs14133049"/>
+    <hyperlink ref="L40" ns1:id="rId39" display="10.1145/3571733"/>
+    <hyperlink ref="L41" ns1:id="rId40" display="10.1109/ACCESS.2019.2953326"/>
+    <hyperlink ref="L42" ns1:id="rId41" display="10.3390/jmse11112065"/>
+    <hyperlink ref="L43" ns1:id="rId42" display="10.1016/j.oceaneng.2022.110749"/>
+    <hyperlink ref="L44" ns1:id="rId43" display="10.1016/j.oceaneng.2022.110531"/>
+    <hyperlink ref="L45" ns1:id="rId44" display="10.3233/ica-210649"/>
+    <hyperlink ref="L46" ns1:id="rId45" display="10.1007/s13437-022-00277-z"/>
+    <hyperlink ref="L47" ns1:id="rId46" display="10.1016/j.ocecoaman.2023.106515"/>
+    <hyperlink ref="L48" ns1:id="rId47" display="10.1016/j.neucom.2015.12.028"/>
+    <hyperlink ref="L49" ns1:id="rId48" display="10.1016/j.oceaneng.2022.111847"/>
+    <hyperlink ref="L50" ns1:id="rId49" display="10.1109/TITS.2020.2976567"/>
+    <hyperlink ref="L51" ns1:id="rId50" display="10.1016/j.oceaneng.2021.109147"/>
+    <hyperlink ref="L52" ns1:id="rId51" display="10.1177/1748006X211051829"/>
+    <hyperlink ref="L53" ns1:id="rId52" display="10.3390/su14010198"/>
+    <hyperlink ref="L54" ns1:id="rId53" display="10.1016/j.ocecoaman.2023.106689"/>
+    <hyperlink ref="L55" ns1:id="rId54" display="10.1109/IROS40897.2019.8968131"/>
+    <hyperlink ref="L56" ns1:id="rId55" display="10.1016/j.oceaneng.2023.114156"/>
+    <hyperlink ref="L57" ns1:id="rId56" display="10.1109/TITS.2022.3151826"/>
+    <hyperlink ref="L58" ns1:id="rId57" display="10.1016/j.oceaneng.2021.108569"/>
+    <hyperlink ref="L59" ns1:id="rId58" display="10.1016/j.ress.2019.106584"/>
+    <hyperlink ref="L60" ns1:id="rId59" display="10.1109/ACCESS.2020.3022600"/>
+    <hyperlink ref="L61" ns1:id="rId60" display="10.1016/j.apor.2021.102755"/>
+    <hyperlink ref="L62" ns1:id="rId61" display="10.1016/j.oceaneng.2020.107913"/>
+    <hyperlink ref="L63" ns1:id="rId62" display="10.1016/j.ress.2022.108709"/>
+    <hyperlink ref="L64" ns1:id="rId63" display="10.3390/jmse10101460"/>
+    <hyperlink ref="L65" ns1:id="rId64" display="10.1016/j.ress.2021.107806"/>
+    <hyperlink ref="L66" ns1:id="rId65" display="10.1109/ACCESS.2022.3154363"/>
+    <hyperlink ref="L67" ns1:id="rId66" display="10.1016/j.eswa.2023.120825"/>
+    <hyperlink ref="L68" ns1:id="rId67" display="10.1016/j.ssci.2020.104758"/>
+    <hyperlink ref="L69" ns1:id="rId68" display="10.3390/jmse10010003"/>
+    <hyperlink ref="L70" ns1:id="rId69" display="10.3390/rs14164070"/>
+    <hyperlink ref="L71" ns1:id="rId70" display="10.1016/j.ssci.2020.104919"/>
+    <hyperlink ref="L72" ns1:id="rId71" display="10.1016/j.neucom.2025.132597"/>
+    <hyperlink ref="L73" ns1:id="rId72" display="10.1109/TITS.2024.3415772"/>
+    <hyperlink ref="L74" ns1:id="rId73" display="10.1016/j.engappai.2023.107513"/>
+    <hyperlink ref="L75" ns1:id="rId74" display="10.1109/TIV.2023.3317336"/>
+    <hyperlink ref="L76" ns1:id="rId75" display="10.1016/j.aei.2025.103355"/>
+    <hyperlink ref="L77" ns1:id="rId76" display="10.1016/j.oceaneng.2025.120907"/>
+    <hyperlink ref="L78" ns1:id="rId77" display="10.1109/TVT.2023.3338518"/>
+    <hyperlink ref="L79" ns1:id="rId78" display="10.1016/j.oceaneng.2024.117210"/>
+    <hyperlink ref="L80" ns1:id="rId79" display="10.1016/j.oceaneng.2026.124487"/>
+    <hyperlink ref="L81" ns1:id="rId80" display="10.21278/brod77204"/>
+    <hyperlink ref="L82" ns1:id="rId81" display="10.1016/j.eswa.2024.124388"/>
+    <hyperlink ref="L83" ns1:id="rId82" display="10.1016/j.tre.2023.103367"/>
+    <hyperlink ref="L84" ns1:id="rId83" display="10.1109/TCYB.2025.3556042"/>
+    <hyperlink ref="L85" ns1:id="rId84" display="10.1016/j.oceaneng.2024.120128"/>
+    <hyperlink ref="L86" ns1:id="rId85" display="10.1016/j.oceaneng.2025.124120"/>
+    <hyperlink ref="L87" ns1:id="rId86" display="10.1007/S10346-024-02337-2"/>
+    <hyperlink ref="L88" ns1:id="rId87" display="10.1109/TASE.2024.3375300"/>
+    <hyperlink ref="L89" ns1:id="rId88" display="10.1016/j.oceaneng.2025.120335"/>
+    <hyperlink ref="L90" ns1:id="rId89" display="10.1016/j.ress.2024.110080"/>
+    <hyperlink ref="L91" ns1:id="rId90" display="10.1109/TVT.2024.3384570"/>
+    <hyperlink ref="L92" ns1:id="rId91" display="10.1016/j.engappai.2023.107625"/>
+    <hyperlink ref="L93" ns1:id="rId92" display="10.1109/JIOT.2023.3325234"/>
+    <hyperlink ref="L94" ns1:id="rId93" display="10.1016/j.asoc.2025.113416"/>
+    <hyperlink ref="L95" ns1:id="rId94" display="10.1016/j.ress.2024.110547"/>
+    <hyperlink ref="L96" ns1:id="rId95" display="10.1016/j.knosys.2024.112205"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -21361,12 +23853,12 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId96"/>
+  <drawing ns1:id="rId96"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -21521,9 +24013,21 @@
       <c r="M3" s="7" t="s">
         <v>1851</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urban Traffic Monitoring &amp; Analysis Using UAVs (traffic-monitoring review)</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
@@ -21653,9 +24157,21 @@
       <c r="M6" s="7" t="s">
         <v>1868</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advances of UAVs toward Future Transportation (state-of-the-art, on-topic)</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
@@ -21697,9 +24213,21 @@
       <c r="M7" s="7" t="s">
         <v>1874</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drone Detection &amp; Classification review (air-perception background; detection half)</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
@@ -21871,9 +24399,21 @@
       <c r="M11" s="7" t="s">
         <v>1895</v>
       </c>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UAS: Current State / U-space (UTM/airspace background)</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
@@ -21959,9 +24499,21 @@
       <c r="M13" s="7" t="s">
         <v>1907</v>
       </c>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Survey of maritime unmanned search system (SAR background)</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
@@ -22003,9 +24555,21 @@
       <c r="M14" s="7" t="s">
         <v>1912</v>
       </c>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Include</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risk/safety/reliability of autonomous ships (MASS formal-safety background)</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
@@ -22116,21 +24680,21 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" display="10.1016/j.comcom.2020.02.069"/>
-    <hyperlink ref="L3" r:id="rId2" display="10.3390/rs14030620"/>
-    <hyperlink ref="L4" r:id="rId3" display="10.1016/j.jestch.2023.101455"/>
-    <hyperlink ref="L5" r:id="rId4" display="10.3390/ijerph18115940"/>
-    <hyperlink ref="L6" r:id="rId5" display="10.3390/futuretransp1020019"/>
-    <hyperlink ref="L7" r:id="rId6" display="10.3390/s24010125"/>
-    <hyperlink ref="L8" r:id="rId7" display="10.1016/j.cosrev.2023.100614"/>
-    <hyperlink ref="L9" r:id="rId8" display="10.3390/rs16050879"/>
-    <hyperlink ref="L10" r:id="rId9" display="10.3390/drones10020091"/>
-    <hyperlink ref="L11" r:id="rId10" display="10.3390/drones9010059"/>
-    <hyperlink ref="L12" r:id="rId11" display="10.1016/j.iswa.2025.200561"/>
-    <hyperlink ref="L13" r:id="rId12" display="10.1016/j.oceaneng.2023.115359"/>
-    <hyperlink ref="L14" r:id="rId13" display="10.1016/j.ssci.2023.106256"/>
-    <hyperlink ref="L15" r:id="rId14" display="10.1016/j.atech.2025.101147"/>
-    <hyperlink ref="L16" r:id="rId15" display="10.1016/j.oceaneng.2024.118174"/>
+    <hyperlink ref="L2" ns1:id="rId1" display="10.1016/j.comcom.2020.02.069"/>
+    <hyperlink ref="L3" ns1:id="rId2" display="10.3390/rs14030620"/>
+    <hyperlink ref="L4" ns1:id="rId3" display="10.1016/j.jestch.2023.101455"/>
+    <hyperlink ref="L5" ns1:id="rId4" display="10.3390/ijerph18115940"/>
+    <hyperlink ref="L6" ns1:id="rId5" display="10.3390/futuretransp1020019"/>
+    <hyperlink ref="L7" ns1:id="rId6" display="10.3390/s24010125"/>
+    <hyperlink ref="L8" ns1:id="rId7" display="10.1016/j.cosrev.2023.100614"/>
+    <hyperlink ref="L9" ns1:id="rId8" display="10.3390/rs16050879"/>
+    <hyperlink ref="L10" ns1:id="rId9" display="10.3390/drones10020091"/>
+    <hyperlink ref="L11" ns1:id="rId10" display="10.3390/drones9010059"/>
+    <hyperlink ref="L12" ns1:id="rId11" display="10.1016/j.iswa.2025.200561"/>
+    <hyperlink ref="L13" ns1:id="rId12" display="10.1016/j.oceaneng.2023.115359"/>
+    <hyperlink ref="L14" ns1:id="rId13" display="10.1016/j.ssci.2023.106256"/>
+    <hyperlink ref="L15" ns1:id="rId14" display="10.1016/j.atech.2025.101147"/>
+    <hyperlink ref="L16" ns1:id="rId15" display="10.1016/j.oceaneng.2024.118174"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22139,7 +24703,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId16"/>
+  <drawing ns1:id="rId16"/>
 </worksheet>
 </file>
 
